--- a/backend/otro.xlsx
+++ b/backend/otro.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fiduprevisora-my.sharepoint.com/personal/p_scorrea_fiduprevisora_com_co/Documents/Escritorio/contratos-dashboard/backend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="8_{124AC31D-8F94-41B4-BB91-46C4C59DB29F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61AC58EA-70A1-4200-93F0-6F72525950E8}"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="8_{124AC31D-8F94-41B4-BB91-46C4C59DB29F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E6D8DAB-7878-40AC-BD83-3F3E44EE2A76}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -936,12 +936,6 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>XPERTASOFT LTDA</t>
-  </si>
-  <si>
-    <t>PRESTACION DE SERVICIOS</t>
-  </si>
-  <si>
     <t>El CONTRATISTA con autonomía técnica y administrativa, se obliga con el CONTRATANTE a prestar los servicios de soporte, actualización y mantenimiento del aplicativo MITRA y la plataforma JAC versión ONPREMISE ESTANDAR, como también migración, implementación, soporte, actualización y mantenimiento del aplicativo MITRA Clúster SaaS, los cuales permiten realizar la integración entre el aplicativo MITRA y la Bolsa de Valores de Colombia. Lo anterior, de conformidad con la propuesta presentada por el CONTRATISTA, la cual hace parte integral del presente CONTRATO, en lo que no contravenga las disposiciones pactadas en el mismo.</t>
   </si>
   <si>
@@ -1096,16 +1090,22 @@
     <t>JUAN ANTONIO URIBE URIBE</t>
   </si>
   <si>
-    <t>WILLIAM</t>
-  </si>
-  <si>
-    <t>1-9000-147-2025</t>
-  </si>
-  <si>
     <t>0211320108_0005</t>
   </si>
   <si>
     <t>MANTENIMIENTO DEL SOFTWARE</t>
+  </si>
+  <si>
+    <t>SOFT SAS</t>
+  </si>
+  <si>
+    <t>SEBAS</t>
+  </si>
+  <si>
+    <t>CONTRATO TEMPORAL</t>
+  </si>
+  <si>
+    <t>1-9000-160-2025</t>
   </si>
 </sst>
 </file>
@@ -1118,7 +1118,7 @@
     <numFmt numFmtId="165" formatCode="_-[$$-240A]\ * #,##0.00_ ;_-[$$-240A]\ * \-#,##0.00\ ;_-[$$-240A]\ * &quot;-&quot;??_ ;_-@_ "/>
     <numFmt numFmtId="166" formatCode="_([$$-240A]\ * #,##0.00_);_([$$-240A]\ * \(#,##0.00\);_([$$-240A]\ * &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="31" x14ac:knownFonts="1">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1321,6 +1321,19 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -2415,7 +2428,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="29" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="407">
+  <cellXfs count="408">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2960,13 +2973,13 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3229,6 +3242,12 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3293,9 +3312,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4143,53 +4159,53 @@
       <c r="G2" s="17"/>
       <c r="H2" s="17"/>
       <c r="I2" s="17"/>
-      <c r="J2" s="299" t="s">
+      <c r="J2" s="300" t="s">
         <v>56</v>
       </c>
-      <c r="K2" s="299"/>
-      <c r="L2" s="299"/>
-      <c r="M2" s="299"/>
-      <c r="N2" s="299"/>
-      <c r="O2" s="299"/>
-      <c r="P2" s="299"/>
-      <c r="Q2" s="299"/>
-      <c r="R2" s="299"/>
-      <c r="S2" s="299"/>
-      <c r="T2" s="299"/>
-      <c r="U2" s="299"/>
-      <c r="V2" s="299"/>
-      <c r="W2" s="299"/>
-      <c r="X2" s="299"/>
-      <c r="Y2" s="299"/>
-      <c r="Z2" s="299"/>
-      <c r="AA2" s="299"/>
-      <c r="AB2" s="299"/>
-      <c r="AC2" s="299"/>
-      <c r="AD2" s="299"/>
-      <c r="AE2" s="299"/>
-      <c r="AF2" s="299"/>
-      <c r="AG2" s="299"/>
-      <c r="AH2" s="299"/>
-      <c r="AI2" s="299"/>
-      <c r="AJ2" s="299"/>
-      <c r="AK2" s="299"/>
+      <c r="K2" s="300"/>
+      <c r="L2" s="300"/>
+      <c r="M2" s="300"/>
+      <c r="N2" s="300"/>
+      <c r="O2" s="300"/>
+      <c r="P2" s="300"/>
+      <c r="Q2" s="300"/>
+      <c r="R2" s="300"/>
+      <c r="S2" s="300"/>
+      <c r="T2" s="300"/>
+      <c r="U2" s="300"/>
+      <c r="V2" s="300"/>
+      <c r="W2" s="300"/>
+      <c r="X2" s="300"/>
+      <c r="Y2" s="300"/>
+      <c r="Z2" s="300"/>
+      <c r="AA2" s="300"/>
+      <c r="AB2" s="300"/>
+      <c r="AC2" s="300"/>
+      <c r="AD2" s="300"/>
+      <c r="AE2" s="300"/>
+      <c r="AF2" s="300"/>
+      <c r="AG2" s="300"/>
+      <c r="AH2" s="300"/>
+      <c r="AI2" s="300"/>
+      <c r="AJ2" s="300"/>
+      <c r="AK2" s="300"/>
       <c r="AL2" s="36"/>
       <c r="AM2" s="17"/>
       <c r="AN2" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="AO2" s="293">
+      <c r="AO2" s="295">
         <v>16</v>
       </c>
-      <c r="AP2" s="294"/>
-      <c r="AQ2" s="290">
+      <c r="AP2" s="296"/>
+      <c r="AQ2" s="292">
         <v>1</v>
       </c>
-      <c r="AR2" s="292"/>
-      <c r="AS2" s="290">
+      <c r="AR2" s="294"/>
+      <c r="AS2" s="292">
         <v>2026</v>
       </c>
-      <c r="AT2" s="291"/>
+      <c r="AT2" s="293"/>
       <c r="AU2" s="14"/>
     </row>
     <row r="3" spans="1:47" ht="12.65" customHeight="1" x14ac:dyDescent="0.35">
@@ -4202,34 +4218,34 @@
       <c r="G3" s="17"/>
       <c r="H3" s="17"/>
       <c r="I3" s="17"/>
-      <c r="J3" s="299"/>
-      <c r="K3" s="299"/>
-      <c r="L3" s="299"/>
-      <c r="M3" s="299"/>
-      <c r="N3" s="299"/>
-      <c r="O3" s="299"/>
-      <c r="P3" s="299"/>
-      <c r="Q3" s="299"/>
-      <c r="R3" s="299"/>
-      <c r="S3" s="299"/>
-      <c r="T3" s="299"/>
-      <c r="U3" s="299"/>
-      <c r="V3" s="299"/>
-      <c r="W3" s="299"/>
-      <c r="X3" s="299"/>
-      <c r="Y3" s="299"/>
-      <c r="Z3" s="299"/>
-      <c r="AA3" s="299"/>
-      <c r="AB3" s="299"/>
-      <c r="AC3" s="299"/>
-      <c r="AD3" s="299"/>
-      <c r="AE3" s="299"/>
-      <c r="AF3" s="299"/>
-      <c r="AG3" s="299"/>
-      <c r="AH3" s="299"/>
-      <c r="AI3" s="299"/>
-      <c r="AJ3" s="299"/>
-      <c r="AK3" s="299"/>
+      <c r="J3" s="300"/>
+      <c r="K3" s="300"/>
+      <c r="L3" s="300"/>
+      <c r="M3" s="300"/>
+      <c r="N3" s="300"/>
+      <c r="O3" s="300"/>
+      <c r="P3" s="300"/>
+      <c r="Q3" s="300"/>
+      <c r="R3" s="300"/>
+      <c r="S3" s="300"/>
+      <c r="T3" s="300"/>
+      <c r="U3" s="300"/>
+      <c r="V3" s="300"/>
+      <c r="W3" s="300"/>
+      <c r="X3" s="300"/>
+      <c r="Y3" s="300"/>
+      <c r="Z3" s="300"/>
+      <c r="AA3" s="300"/>
+      <c r="AB3" s="300"/>
+      <c r="AC3" s="300"/>
+      <c r="AD3" s="300"/>
+      <c r="AE3" s="300"/>
+      <c r="AF3" s="300"/>
+      <c r="AG3" s="300"/>
+      <c r="AH3" s="300"/>
+      <c r="AI3" s="300"/>
+      <c r="AJ3" s="300"/>
+      <c r="AK3" s="300"/>
       <c r="AL3" s="17"/>
       <c r="AM3" s="17"/>
       <c r="AN3" s="26"/>
@@ -4401,28 +4417,28 @@
       <c r="F7" s="223"/>
       <c r="G7" s="223"/>
       <c r="H7" s="223"/>
-      <c r="I7" s="275" t="s">
-        <v>147</v>
-      </c>
-      <c r="J7" s="275"/>
-      <c r="K7" s="275"/>
-      <c r="L7" s="275"/>
-      <c r="M7" s="275"/>
-      <c r="N7" s="275"/>
-      <c r="O7" s="275"/>
-      <c r="P7" s="275"/>
-      <c r="Q7" s="275"/>
-      <c r="R7" s="275"/>
-      <c r="S7" s="275"/>
-      <c r="T7" s="275"/>
-      <c r="U7" s="275"/>
-      <c r="V7" s="275"/>
-      <c r="W7" s="275"/>
-      <c r="X7" s="275"/>
-      <c r="Y7" s="275"/>
-      <c r="Z7" s="275"/>
-      <c r="AA7" s="275"/>
-      <c r="AB7" s="275"/>
+      <c r="I7" s="276" t="s">
+        <v>148</v>
+      </c>
+      <c r="J7" s="276"/>
+      <c r="K7" s="276"/>
+      <c r="L7" s="276"/>
+      <c r="M7" s="276"/>
+      <c r="N7" s="276"/>
+      <c r="O7" s="276"/>
+      <c r="P7" s="276"/>
+      <c r="Q7" s="276"/>
+      <c r="R7" s="276"/>
+      <c r="S7" s="276"/>
+      <c r="T7" s="276"/>
+      <c r="U7" s="276"/>
+      <c r="V7" s="276"/>
+      <c r="W7" s="276"/>
+      <c r="X7" s="276"/>
+      <c r="Y7" s="276"/>
+      <c r="Z7" s="276"/>
+      <c r="AA7" s="276"/>
+      <c r="AB7" s="276"/>
       <c r="AC7" s="61"/>
       <c r="AD7" s="223" t="s">
         <v>5</v>
@@ -4433,18 +4449,18 @@
       <c r="AH7" s="223"/>
       <c r="AI7" s="223"/>
       <c r="AJ7" s="223"/>
-      <c r="AK7" s="295" t="s">
-        <v>144</v>
-      </c>
-      <c r="AL7" s="295"/>
-      <c r="AM7" s="295"/>
-      <c r="AN7" s="295"/>
-      <c r="AO7" s="295"/>
-      <c r="AP7" s="295"/>
-      <c r="AQ7" s="295"/>
-      <c r="AR7" s="295"/>
-      <c r="AS7" s="295"/>
-      <c r="AT7" s="295"/>
+      <c r="AK7" s="297" t="s">
+        <v>142</v>
+      </c>
+      <c r="AL7" s="297"/>
+      <c r="AM7" s="297"/>
+      <c r="AN7" s="297"/>
+      <c r="AO7" s="297"/>
+      <c r="AP7" s="297"/>
+      <c r="AQ7" s="297"/>
+      <c r="AR7" s="297"/>
+      <c r="AS7" s="297"/>
+      <c r="AT7" s="297"/>
       <c r="AU7" s="62"/>
     </row>
     <row r="8" spans="1:47" s="63" customFormat="1" ht="12.65" customHeight="1" x14ac:dyDescent="0.35">
@@ -4458,50 +4474,50 @@
       <c r="F8" s="223"/>
       <c r="G8" s="223"/>
       <c r="H8" s="223"/>
-      <c r="I8" s="298" t="s">
-        <v>148</v>
-      </c>
-      <c r="J8" s="298"/>
-      <c r="K8" s="298"/>
-      <c r="L8" s="298"/>
-      <c r="M8" s="298"/>
-      <c r="N8" s="298"/>
-      <c r="O8" s="298"/>
-      <c r="P8" s="298"/>
-      <c r="Q8" s="298"/>
-      <c r="R8" s="298"/>
-      <c r="S8" s="298"/>
-      <c r="T8" s="298"/>
-      <c r="U8" s="298"/>
-      <c r="V8" s="298"/>
-      <c r="W8" s="298"/>
-      <c r="X8" s="298"/>
-      <c r="Y8" s="298"/>
-      <c r="Z8" s="298"/>
-      <c r="AA8" s="298"/>
-      <c r="AB8" s="298"/>
+      <c r="I8" s="277" t="s">
+        <v>150</v>
+      </c>
+      <c r="J8" s="277"/>
+      <c r="K8" s="277"/>
+      <c r="L8" s="277"/>
+      <c r="M8" s="277"/>
+      <c r="N8" s="277"/>
+      <c r="O8" s="277"/>
+      <c r="P8" s="277"/>
+      <c r="Q8" s="277"/>
+      <c r="R8" s="277"/>
+      <c r="S8" s="277"/>
+      <c r="T8" s="277"/>
+      <c r="U8" s="277"/>
+      <c r="V8" s="277"/>
+      <c r="W8" s="277"/>
+      <c r="X8" s="277"/>
+      <c r="Y8" s="277"/>
+      <c r="Z8" s="277"/>
+      <c r="AA8" s="277"/>
+      <c r="AB8" s="277"/>
       <c r="AC8" s="64"/>
-      <c r="AD8" s="296" t="s">
+      <c r="AD8" s="298" t="s">
         <v>73</v>
       </c>
-      <c r="AE8" s="296"/>
-      <c r="AF8" s="296"/>
-      <c r="AG8" s="296"/>
-      <c r="AH8" s="296"/>
-      <c r="AI8" s="296"/>
-      <c r="AJ8" s="297"/>
-      <c r="AK8" s="277" t="s">
-        <v>103</v>
-      </c>
-      <c r="AL8" s="277"/>
-      <c r="AM8" s="277"/>
-      <c r="AN8" s="277"/>
-      <c r="AO8" s="277"/>
-      <c r="AP8" s="277"/>
-      <c r="AQ8" s="277"/>
-      <c r="AR8" s="277"/>
-      <c r="AS8" s="277"/>
-      <c r="AT8" s="278"/>
+      <c r="AE8" s="298"/>
+      <c r="AF8" s="298"/>
+      <c r="AG8" s="298"/>
+      <c r="AH8" s="298"/>
+      <c r="AI8" s="298"/>
+      <c r="AJ8" s="299"/>
+      <c r="AK8" s="279" t="s">
+        <v>149</v>
+      </c>
+      <c r="AL8" s="279"/>
+      <c r="AM8" s="279"/>
+      <c r="AN8" s="279"/>
+      <c r="AO8" s="279"/>
+      <c r="AP8" s="279"/>
+      <c r="AQ8" s="279"/>
+      <c r="AR8" s="279"/>
+      <c r="AS8" s="279"/>
+      <c r="AT8" s="280"/>
       <c r="AU8" s="62"/>
     </row>
     <row r="9" spans="1:47" s="63" customFormat="1" ht="12.65" customHeight="1" x14ac:dyDescent="0.35">
@@ -4515,28 +4531,28 @@
       <c r="F9" s="223"/>
       <c r="G9" s="223"/>
       <c r="H9" s="223"/>
-      <c r="I9" s="275" t="s">
-        <v>102</v>
-      </c>
-      <c r="J9" s="275"/>
-      <c r="K9" s="275"/>
-      <c r="L9" s="275"/>
-      <c r="M9" s="275"/>
-      <c r="N9" s="275"/>
-      <c r="O9" s="275"/>
-      <c r="P9" s="275"/>
-      <c r="Q9" s="275"/>
-      <c r="R9" s="275"/>
-      <c r="S9" s="275"/>
-      <c r="T9" s="275"/>
-      <c r="U9" s="275"/>
-      <c r="V9" s="275"/>
-      <c r="W9" s="275"/>
-      <c r="X9" s="275"/>
-      <c r="Y9" s="275"/>
-      <c r="Z9" s="275"/>
-      <c r="AA9" s="275"/>
-      <c r="AB9" s="275"/>
+      <c r="I9" s="276" t="s">
+        <v>147</v>
+      </c>
+      <c r="J9" s="276"/>
+      <c r="K9" s="276"/>
+      <c r="L9" s="276"/>
+      <c r="M9" s="276"/>
+      <c r="N9" s="276"/>
+      <c r="O9" s="276"/>
+      <c r="P9" s="276"/>
+      <c r="Q9" s="276"/>
+      <c r="R9" s="276"/>
+      <c r="S9" s="276"/>
+      <c r="T9" s="276"/>
+      <c r="U9" s="276"/>
+      <c r="V9" s="276"/>
+      <c r="W9" s="276"/>
+      <c r="X9" s="276"/>
+      <c r="Y9" s="276"/>
+      <c r="Z9" s="276"/>
+      <c r="AA9" s="276"/>
+      <c r="AB9" s="276"/>
       <c r="AC9" s="64"/>
       <c r="AD9" s="65" t="s">
         <v>34</v>
@@ -4549,22 +4565,22 @@
         <v>13</v>
       </c>
       <c r="AH9" s="66"/>
-      <c r="AI9" s="279" t="s">
+      <c r="AI9" s="281" t="s">
         <v>3</v>
       </c>
-      <c r="AJ9" s="280"/>
-      <c r="AK9" s="276" t="s">
-        <v>145</v>
-      </c>
-      <c r="AL9" s="277"/>
-      <c r="AM9" s="277"/>
-      <c r="AN9" s="277"/>
-      <c r="AO9" s="277"/>
-      <c r="AP9" s="277"/>
-      <c r="AQ9" s="277"/>
-      <c r="AR9" s="277"/>
-      <c r="AS9" s="277"/>
-      <c r="AT9" s="278"/>
+      <c r="AJ9" s="282"/>
+      <c r="AK9" s="278" t="s">
+        <v>143</v>
+      </c>
+      <c r="AL9" s="279"/>
+      <c r="AM9" s="279"/>
+      <c r="AN9" s="279"/>
+      <c r="AO9" s="279"/>
+      <c r="AP9" s="279"/>
+      <c r="AQ9" s="279"/>
+      <c r="AR9" s="279"/>
+      <c r="AS9" s="279"/>
+      <c r="AT9" s="280"/>
       <c r="AU9" s="62"/>
     </row>
     <row r="10" spans="1:47" s="63" customFormat="1" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
@@ -4578,28 +4594,28 @@
       <c r="F10" s="223"/>
       <c r="G10" s="223"/>
       <c r="H10" s="223"/>
-      <c r="I10" s="275" t="s">
-        <v>146</v>
-      </c>
-      <c r="J10" s="275"/>
-      <c r="K10" s="275"/>
-      <c r="L10" s="275"/>
-      <c r="M10" s="275"/>
-      <c r="N10" s="275"/>
-      <c r="O10" s="275"/>
-      <c r="P10" s="275"/>
-      <c r="Q10" s="275"/>
-      <c r="R10" s="275"/>
-      <c r="S10" s="275"/>
-      <c r="T10" s="275"/>
-      <c r="U10" s="275"/>
-      <c r="V10" s="275"/>
-      <c r="W10" s="275"/>
-      <c r="X10" s="275"/>
-      <c r="Y10" s="275"/>
-      <c r="Z10" s="275"/>
-      <c r="AA10" s="275"/>
-      <c r="AB10" s="275"/>
+      <c r="I10" s="276" t="s">
+        <v>144</v>
+      </c>
+      <c r="J10" s="276"/>
+      <c r="K10" s="276"/>
+      <c r="L10" s="276"/>
+      <c r="M10" s="276"/>
+      <c r="N10" s="276"/>
+      <c r="O10" s="276"/>
+      <c r="P10" s="276"/>
+      <c r="Q10" s="276"/>
+      <c r="R10" s="276"/>
+      <c r="S10" s="276"/>
+      <c r="T10" s="276"/>
+      <c r="U10" s="276"/>
+      <c r="V10" s="276"/>
+      <c r="W10" s="276"/>
+      <c r="X10" s="276"/>
+      <c r="Y10" s="276"/>
+      <c r="Z10" s="276"/>
+      <c r="AA10" s="276"/>
+      <c r="AB10" s="276"/>
       <c r="AC10" s="64"/>
       <c r="AD10" s="67"/>
       <c r="AE10" s="67"/>
@@ -4610,22 +4626,22 @@
       <c r="AH10" s="70" t="s">
         <v>100</v>
       </c>
-      <c r="AI10" s="280" t="s">
+      <c r="AI10" s="282" t="s">
         <v>3</v>
       </c>
-      <c r="AJ10" s="280"/>
-      <c r="AK10" s="276">
+      <c r="AJ10" s="282"/>
+      <c r="AK10" s="278">
         <v>94402876</v>
       </c>
-      <c r="AL10" s="277"/>
-      <c r="AM10" s="277"/>
-      <c r="AN10" s="277"/>
-      <c r="AO10" s="277"/>
-      <c r="AP10" s="277"/>
-      <c r="AQ10" s="277"/>
-      <c r="AR10" s="277"/>
-      <c r="AS10" s="277"/>
-      <c r="AT10" s="278"/>
+      <c r="AL10" s="279"/>
+      <c r="AM10" s="279"/>
+      <c r="AN10" s="279"/>
+      <c r="AO10" s="279"/>
+      <c r="AP10" s="279"/>
+      <c r="AQ10" s="279"/>
+      <c r="AR10" s="279"/>
+      <c r="AS10" s="279"/>
+      <c r="AT10" s="280"/>
       <c r="AU10" s="62"/>
     </row>
     <row r="11" spans="1:47" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4728,55 +4744,55 @@
     </row>
     <row r="13" spans="1:47" s="63" customFormat="1" ht="12.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="59"/>
-      <c r="B13" s="223" t="s">
+      <c r="B13" s="275" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="223"/>
-      <c r="D13" s="223"/>
-      <c r="E13" s="223"/>
-      <c r="F13" s="223"/>
-      <c r="G13" s="223"/>
-      <c r="H13" s="223"/>
-      <c r="I13" s="281" t="s">
-        <v>104</v>
-      </c>
-      <c r="J13" s="282"/>
-      <c r="K13" s="282"/>
-      <c r="L13" s="282"/>
-      <c r="M13" s="282"/>
-      <c r="N13" s="282"/>
-      <c r="O13" s="282"/>
-      <c r="P13" s="282"/>
-      <c r="Q13" s="282"/>
-      <c r="R13" s="282"/>
-      <c r="S13" s="282"/>
-      <c r="T13" s="282"/>
-      <c r="U13" s="282"/>
-      <c r="V13" s="282"/>
-      <c r="W13" s="282"/>
-      <c r="X13" s="282"/>
-      <c r="Y13" s="282"/>
-      <c r="Z13" s="282"/>
-      <c r="AA13" s="282"/>
-      <c r="AB13" s="282"/>
-      <c r="AC13" s="282"/>
-      <c r="AD13" s="282"/>
-      <c r="AE13" s="282"/>
-      <c r="AF13" s="282"/>
-      <c r="AG13" s="282"/>
-      <c r="AH13" s="282"/>
-      <c r="AI13" s="282"/>
-      <c r="AJ13" s="282"/>
-      <c r="AK13" s="282"/>
-      <c r="AL13" s="282"/>
-      <c r="AM13" s="282"/>
-      <c r="AN13" s="282"/>
-      <c r="AO13" s="282"/>
-      <c r="AP13" s="282"/>
-      <c r="AQ13" s="282"/>
-      <c r="AR13" s="282"/>
-      <c r="AS13" s="282"/>
-      <c r="AT13" s="283"/>
+      <c r="C13" s="275"/>
+      <c r="D13" s="275"/>
+      <c r="E13" s="275"/>
+      <c r="F13" s="275"/>
+      <c r="G13" s="275"/>
+      <c r="H13" s="275"/>
+      <c r="I13" s="283" t="s">
+        <v>102</v>
+      </c>
+      <c r="J13" s="284"/>
+      <c r="K13" s="284"/>
+      <c r="L13" s="284"/>
+      <c r="M13" s="284"/>
+      <c r="N13" s="284"/>
+      <c r="O13" s="284"/>
+      <c r="P13" s="284"/>
+      <c r="Q13" s="284"/>
+      <c r="R13" s="284"/>
+      <c r="S13" s="284"/>
+      <c r="T13" s="284"/>
+      <c r="U13" s="284"/>
+      <c r="V13" s="284"/>
+      <c r="W13" s="284"/>
+      <c r="X13" s="284"/>
+      <c r="Y13" s="284"/>
+      <c r="Z13" s="284"/>
+      <c r="AA13" s="284"/>
+      <c r="AB13" s="284"/>
+      <c r="AC13" s="284"/>
+      <c r="AD13" s="284"/>
+      <c r="AE13" s="284"/>
+      <c r="AF13" s="284"/>
+      <c r="AG13" s="284"/>
+      <c r="AH13" s="284"/>
+      <c r="AI13" s="284"/>
+      <c r="AJ13" s="284"/>
+      <c r="AK13" s="284"/>
+      <c r="AL13" s="284"/>
+      <c r="AM13" s="284"/>
+      <c r="AN13" s="284"/>
+      <c r="AO13" s="284"/>
+      <c r="AP13" s="284"/>
+      <c r="AQ13" s="284"/>
+      <c r="AR13" s="284"/>
+      <c r="AS13" s="284"/>
+      <c r="AT13" s="285"/>
       <c r="AU13" s="62"/>
     </row>
     <row r="14" spans="1:47" s="63" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.35">
@@ -4788,44 +4804,44 @@
       <c r="F14" s="60"/>
       <c r="G14" s="60"/>
       <c r="H14" s="60"/>
-      <c r="I14" s="284"/>
-      <c r="J14" s="285"/>
-      <c r="K14" s="285"/>
-      <c r="L14" s="285"/>
-      <c r="M14" s="285"/>
-      <c r="N14" s="285"/>
-      <c r="O14" s="285"/>
-      <c r="P14" s="285"/>
-      <c r="Q14" s="285"/>
-      <c r="R14" s="285"/>
-      <c r="S14" s="285"/>
-      <c r="T14" s="285"/>
-      <c r="U14" s="285"/>
-      <c r="V14" s="285"/>
-      <c r="W14" s="285"/>
-      <c r="X14" s="285"/>
-      <c r="Y14" s="285"/>
-      <c r="Z14" s="285"/>
-      <c r="AA14" s="285"/>
-      <c r="AB14" s="285"/>
-      <c r="AC14" s="285"/>
-      <c r="AD14" s="285"/>
-      <c r="AE14" s="285"/>
-      <c r="AF14" s="285"/>
-      <c r="AG14" s="285"/>
-      <c r="AH14" s="285"/>
-      <c r="AI14" s="285"/>
-      <c r="AJ14" s="285"/>
-      <c r="AK14" s="285"/>
-      <c r="AL14" s="285"/>
-      <c r="AM14" s="285"/>
-      <c r="AN14" s="285"/>
-      <c r="AO14" s="285"/>
-      <c r="AP14" s="285"/>
-      <c r="AQ14" s="285"/>
-      <c r="AR14" s="285"/>
-      <c r="AS14" s="285"/>
-      <c r="AT14" s="286"/>
+      <c r="I14" s="286"/>
+      <c r="J14" s="287"/>
+      <c r="K14" s="287"/>
+      <c r="L14" s="287"/>
+      <c r="M14" s="287"/>
+      <c r="N14" s="287"/>
+      <c r="O14" s="287"/>
+      <c r="P14" s="287"/>
+      <c r="Q14" s="287"/>
+      <c r="R14" s="287"/>
+      <c r="S14" s="287"/>
+      <c r="T14" s="287"/>
+      <c r="U14" s="287"/>
+      <c r="V14" s="287"/>
+      <c r="W14" s="287"/>
+      <c r="X14" s="287"/>
+      <c r="Y14" s="287"/>
+      <c r="Z14" s="287"/>
+      <c r="AA14" s="287"/>
+      <c r="AB14" s="287"/>
+      <c r="AC14" s="287"/>
+      <c r="AD14" s="287"/>
+      <c r="AE14" s="287"/>
+      <c r="AF14" s="287"/>
+      <c r="AG14" s="287"/>
+      <c r="AH14" s="287"/>
+      <c r="AI14" s="287"/>
+      <c r="AJ14" s="287"/>
+      <c r="AK14" s="287"/>
+      <c r="AL14" s="287"/>
+      <c r="AM14" s="287"/>
+      <c r="AN14" s="287"/>
+      <c r="AO14" s="287"/>
+      <c r="AP14" s="287"/>
+      <c r="AQ14" s="287"/>
+      <c r="AR14" s="287"/>
+      <c r="AS14" s="287"/>
+      <c r="AT14" s="288"/>
       <c r="AU14" s="62"/>
     </row>
     <row r="15" spans="1:47" s="63" customFormat="1" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4837,44 +4853,44 @@
       <c r="F15" s="60"/>
       <c r="G15" s="60"/>
       <c r="H15" s="60"/>
-      <c r="I15" s="287"/>
-      <c r="J15" s="288"/>
-      <c r="K15" s="288"/>
-      <c r="L15" s="288"/>
-      <c r="M15" s="288"/>
-      <c r="N15" s="288"/>
-      <c r="O15" s="288"/>
-      <c r="P15" s="288"/>
-      <c r="Q15" s="288"/>
-      <c r="R15" s="288"/>
-      <c r="S15" s="288"/>
-      <c r="T15" s="288"/>
-      <c r="U15" s="288"/>
-      <c r="V15" s="288"/>
-      <c r="W15" s="288"/>
-      <c r="X15" s="288"/>
-      <c r="Y15" s="288"/>
-      <c r="Z15" s="288"/>
-      <c r="AA15" s="288"/>
-      <c r="AB15" s="288"/>
-      <c r="AC15" s="288"/>
-      <c r="AD15" s="288"/>
-      <c r="AE15" s="288"/>
-      <c r="AF15" s="288"/>
-      <c r="AG15" s="288"/>
-      <c r="AH15" s="288"/>
-      <c r="AI15" s="288"/>
-      <c r="AJ15" s="288"/>
-      <c r="AK15" s="288"/>
-      <c r="AL15" s="288"/>
-      <c r="AM15" s="288"/>
-      <c r="AN15" s="288"/>
-      <c r="AO15" s="288"/>
-      <c r="AP15" s="288"/>
-      <c r="AQ15" s="288"/>
-      <c r="AR15" s="288"/>
-      <c r="AS15" s="288"/>
-      <c r="AT15" s="289"/>
+      <c r="I15" s="289"/>
+      <c r="J15" s="290"/>
+      <c r="K15" s="290"/>
+      <c r="L15" s="290"/>
+      <c r="M15" s="290"/>
+      <c r="N15" s="290"/>
+      <c r="O15" s="290"/>
+      <c r="P15" s="290"/>
+      <c r="Q15" s="290"/>
+      <c r="R15" s="290"/>
+      <c r="S15" s="290"/>
+      <c r="T15" s="290"/>
+      <c r="U15" s="290"/>
+      <c r="V15" s="290"/>
+      <c r="W15" s="290"/>
+      <c r="X15" s="290"/>
+      <c r="Y15" s="290"/>
+      <c r="Z15" s="290"/>
+      <c r="AA15" s="290"/>
+      <c r="AB15" s="290"/>
+      <c r="AC15" s="290"/>
+      <c r="AD15" s="290"/>
+      <c r="AE15" s="290"/>
+      <c r="AF15" s="290"/>
+      <c r="AG15" s="290"/>
+      <c r="AH15" s="290"/>
+      <c r="AI15" s="290"/>
+      <c r="AJ15" s="290"/>
+      <c r="AK15" s="290"/>
+      <c r="AL15" s="290"/>
+      <c r="AM15" s="290"/>
+      <c r="AN15" s="290"/>
+      <c r="AO15" s="290"/>
+      <c r="AP15" s="290"/>
+      <c r="AQ15" s="290"/>
+      <c r="AR15" s="290"/>
+      <c r="AS15" s="290"/>
+      <c r="AT15" s="291"/>
       <c r="AU15" s="62"/>
     </row>
     <row r="16" spans="1:47" s="63" customFormat="1" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -5314,7 +5330,7 @@
       <c r="F24" s="243"/>
       <c r="G24" s="244"/>
       <c r="H24" s="267" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I24" s="243"/>
       <c r="J24" s="243"/>
@@ -5792,25 +5808,25 @@
       <c r="F32" s="141"/>
       <c r="G32" s="141"/>
       <c r="H32" s="141"/>
-      <c r="I32" s="305" t="s">
+      <c r="I32" s="306" t="s">
         <v>16</v>
       </c>
-      <c r="J32" s="305"/>
-      <c r="K32" s="306"/>
+      <c r="J32" s="306"/>
+      <c r="K32" s="307"/>
       <c r="L32" s="87"/>
-      <c r="M32" s="307" t="s">
+      <c r="M32" s="308" t="s">
         <v>17</v>
       </c>
-      <c r="N32" s="308"/>
-      <c r="O32" s="308"/>
-      <c r="P32" s="308"/>
+      <c r="N32" s="309"/>
+      <c r="O32" s="309"/>
+      <c r="P32" s="309"/>
       <c r="Q32" s="87"/>
-      <c r="R32" s="309" t="s">
+      <c r="R32" s="310" t="s">
         <v>18</v>
       </c>
-      <c r="S32" s="310"/>
-      <c r="T32" s="310"/>
-      <c r="U32" s="307"/>
+      <c r="S32" s="311"/>
+      <c r="T32" s="311"/>
+      <c r="U32" s="308"/>
       <c r="V32" s="88"/>
       <c r="W32" s="144"/>
       <c r="X32" s="144"/>
@@ -5823,12 +5839,12 @@
       <c r="AE32" s="141"/>
       <c r="AF32" s="141"/>
       <c r="AG32" s="240"/>
-      <c r="AH32" s="311"/>
-      <c r="AI32" s="312"/>
-      <c r="AJ32" s="312"/>
-      <c r="AK32" s="312"/>
-      <c r="AL32" s="312"/>
-      <c r="AM32" s="313"/>
+      <c r="AH32" s="312"/>
+      <c r="AI32" s="313"/>
+      <c r="AJ32" s="313"/>
+      <c r="AK32" s="313"/>
+      <c r="AL32" s="313"/>
+      <c r="AM32" s="314"/>
       <c r="AN32" s="235"/>
       <c r="AO32" s="235"/>
       <c r="AP32" s="235"/>
@@ -6048,38 +6064,38 @@
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
-      <c r="J37" s="302">
+      <c r="J37" s="303">
         <f>+AN24</f>
         <v>386128219</v>
       </c>
-      <c r="K37" s="302"/>
-      <c r="L37" s="302"/>
-      <c r="M37" s="302"/>
-      <c r="N37" s="302"/>
-      <c r="O37" s="302"/>
-      <c r="P37" s="302"/>
-      <c r="Q37" s="302"/>
-      <c r="R37" s="302"/>
-      <c r="S37" s="302"/>
-      <c r="T37" s="302"/>
-      <c r="U37" s="302"/>
-      <c r="V37" s="302"/>
-      <c r="W37" s="302"/>
-      <c r="X37" s="302"/>
-      <c r="Y37" s="302"/>
-      <c r="Z37" s="302"/>
-      <c r="AA37" s="302"/>
-      <c r="AB37" s="302"/>
-      <c r="AC37" s="302"/>
-      <c r="AD37" s="302"/>
-      <c r="AE37" s="302"/>
-      <c r="AF37" s="302"/>
-      <c r="AG37" s="302"/>
-      <c r="AH37" s="302"/>
-      <c r="AI37" s="302"/>
-      <c r="AJ37" s="302"/>
-      <c r="AK37" s="302"/>
-      <c r="AL37" s="302"/>
+      <c r="K37" s="303"/>
+      <c r="L37" s="303"/>
+      <c r="M37" s="303"/>
+      <c r="N37" s="303"/>
+      <c r="O37" s="303"/>
+      <c r="P37" s="303"/>
+      <c r="Q37" s="303"/>
+      <c r="R37" s="303"/>
+      <c r="S37" s="303"/>
+      <c r="T37" s="303"/>
+      <c r="U37" s="303"/>
+      <c r="V37" s="303"/>
+      <c r="W37" s="303"/>
+      <c r="X37" s="303"/>
+      <c r="Y37" s="303"/>
+      <c r="Z37" s="303"/>
+      <c r="AA37" s="303"/>
+      <c r="AB37" s="303"/>
+      <c r="AC37" s="303"/>
+      <c r="AD37" s="303"/>
+      <c r="AE37" s="303"/>
+      <c r="AF37" s="303"/>
+      <c r="AG37" s="303"/>
+      <c r="AH37" s="303"/>
+      <c r="AI37" s="303"/>
+      <c r="AJ37" s="303"/>
+      <c r="AK37" s="303"/>
+      <c r="AL37" s="303"/>
       <c r="AM37" s="2"/>
       <c r="AN37" s="2"/>
       <c r="AO37" s="2"/>
@@ -6197,60 +6213,60 @@
       <c r="B40" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="303" t="s">
+      <c r="C40" s="304" t="s">
         <v>8</v>
       </c>
-      <c r="D40" s="303"/>
-      <c r="E40" s="303"/>
-      <c r="F40" s="303"/>
-      <c r="G40" s="303"/>
-      <c r="H40" s="304"/>
-      <c r="I40" s="300" t="s">
+      <c r="D40" s="304"/>
+      <c r="E40" s="304"/>
+      <c r="F40" s="304"/>
+      <c r="G40" s="304"/>
+      <c r="H40" s="305"/>
+      <c r="I40" s="301" t="s">
         <v>7</v>
       </c>
-      <c r="J40" s="300"/>
-      <c r="K40" s="300"/>
-      <c r="L40" s="300"/>
-      <c r="M40" s="300"/>
-      <c r="N40" s="300"/>
-      <c r="O40" s="300"/>
-      <c r="P40" s="300"/>
-      <c r="Q40" s="314" t="s">
+      <c r="J40" s="301"/>
+      <c r="K40" s="301"/>
+      <c r="L40" s="301"/>
+      <c r="M40" s="301"/>
+      <c r="N40" s="301"/>
+      <c r="O40" s="301"/>
+      <c r="P40" s="301"/>
+      <c r="Q40" s="315" t="s">
         <v>9</v>
       </c>
-      <c r="R40" s="303"/>
-      <c r="S40" s="303"/>
-      <c r="T40" s="303"/>
-      <c r="U40" s="303"/>
-      <c r="V40" s="303"/>
-      <c r="W40" s="304"/>
-      <c r="X40" s="300" t="s">
+      <c r="R40" s="304"/>
+      <c r="S40" s="304"/>
+      <c r="T40" s="304"/>
+      <c r="U40" s="304"/>
+      <c r="V40" s="304"/>
+      <c r="W40" s="305"/>
+      <c r="X40" s="301" t="s">
         <v>10</v>
       </c>
-      <c r="Y40" s="300"/>
-      <c r="Z40" s="300"/>
-      <c r="AA40" s="300"/>
-      <c r="AB40" s="300"/>
-      <c r="AC40" s="300"/>
-      <c r="AD40" s="300"/>
-      <c r="AE40" s="300"/>
-      <c r="AF40" s="300"/>
-      <c r="AG40" s="300"/>
-      <c r="AH40" s="300"/>
-      <c r="AI40" s="300"/>
-      <c r="AJ40" s="300"/>
-      <c r="AK40" s="300"/>
-      <c r="AL40" s="300"/>
-      <c r="AM40" s="300"/>
-      <c r="AN40" s="300" t="s">
+      <c r="Y40" s="301"/>
+      <c r="Z40" s="301"/>
+      <c r="AA40" s="301"/>
+      <c r="AB40" s="301"/>
+      <c r="AC40" s="301"/>
+      <c r="AD40" s="301"/>
+      <c r="AE40" s="301"/>
+      <c r="AF40" s="301"/>
+      <c r="AG40" s="301"/>
+      <c r="AH40" s="301"/>
+      <c r="AI40" s="301"/>
+      <c r="AJ40" s="301"/>
+      <c r="AK40" s="301"/>
+      <c r="AL40" s="301"/>
+      <c r="AM40" s="301"/>
+      <c r="AN40" s="301" t="s">
         <v>11</v>
       </c>
-      <c r="AO40" s="300"/>
-      <c r="AP40" s="300"/>
-      <c r="AQ40" s="300"/>
-      <c r="AR40" s="300"/>
-      <c r="AS40" s="300"/>
-      <c r="AT40" s="301"/>
+      <c r="AO40" s="301"/>
+      <c r="AP40" s="301"/>
+      <c r="AQ40" s="301"/>
+      <c r="AR40" s="301"/>
+      <c r="AS40" s="301"/>
+      <c r="AT40" s="302"/>
       <c r="AU40" s="14"/>
     </row>
     <row r="41" spans="1:47" ht="12.65" customHeight="1" x14ac:dyDescent="0.35">
@@ -6258,60 +6274,60 @@
       <c r="B41" s="58">
         <v>1</v>
       </c>
-      <c r="C41" s="401">
+      <c r="C41" s="402">
         <v>45924</v>
       </c>
-      <c r="D41" s="402"/>
-      <c r="E41" s="402"/>
-      <c r="F41" s="402"/>
-      <c r="G41" s="402"/>
-      <c r="H41" s="403"/>
-      <c r="I41" s="396">
+      <c r="D41" s="403"/>
+      <c r="E41" s="403"/>
+      <c r="F41" s="403"/>
+      <c r="G41" s="403"/>
+      <c r="H41" s="404"/>
+      <c r="I41" s="397">
         <v>11103</v>
       </c>
-      <c r="J41" s="397"/>
-      <c r="K41" s="397"/>
-      <c r="L41" s="397"/>
-      <c r="M41" s="397"/>
-      <c r="N41" s="397"/>
-      <c r="O41" s="397"/>
-      <c r="P41" s="398"/>
-      <c r="Q41" s="317" t="s">
-        <v>107</v>
-      </c>
-      <c r="R41" s="317"/>
-      <c r="S41" s="317"/>
-      <c r="T41" s="317"/>
-      <c r="U41" s="317"/>
-      <c r="V41" s="317"/>
-      <c r="W41" s="317"/>
-      <c r="X41" s="317" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y41" s="317"/>
-      <c r="Z41" s="317"/>
-      <c r="AA41" s="317"/>
-      <c r="AB41" s="317"/>
-      <c r="AC41" s="317"/>
-      <c r="AD41" s="317"/>
-      <c r="AE41" s="317"/>
-      <c r="AF41" s="317"/>
-      <c r="AG41" s="317"/>
-      <c r="AH41" s="317"/>
-      <c r="AI41" s="317"/>
-      <c r="AJ41" s="317"/>
-      <c r="AK41" s="317"/>
-      <c r="AL41" s="317"/>
-      <c r="AM41" s="317"/>
-      <c r="AN41" s="315">
+      <c r="J41" s="398"/>
+      <c r="K41" s="398"/>
+      <c r="L41" s="398"/>
+      <c r="M41" s="398"/>
+      <c r="N41" s="398"/>
+      <c r="O41" s="398"/>
+      <c r="P41" s="399"/>
+      <c r="Q41" s="318" t="s">
+        <v>105</v>
+      </c>
+      <c r="R41" s="318"/>
+      <c r="S41" s="318"/>
+      <c r="T41" s="318"/>
+      <c r="U41" s="318"/>
+      <c r="V41" s="318"/>
+      <c r="W41" s="318"/>
+      <c r="X41" s="318" t="s">
+        <v>106</v>
+      </c>
+      <c r="Y41" s="318"/>
+      <c r="Z41" s="318"/>
+      <c r="AA41" s="318"/>
+      <c r="AB41" s="318"/>
+      <c r="AC41" s="318"/>
+      <c r="AD41" s="318"/>
+      <c r="AE41" s="318"/>
+      <c r="AF41" s="318"/>
+      <c r="AG41" s="318"/>
+      <c r="AH41" s="318"/>
+      <c r="AI41" s="318"/>
+      <c r="AJ41" s="318"/>
+      <c r="AK41" s="318"/>
+      <c r="AL41" s="318"/>
+      <c r="AM41" s="318"/>
+      <c r="AN41" s="316">
         <v>86531419</v>
       </c>
-      <c r="AO41" s="315"/>
-      <c r="AP41" s="315"/>
-      <c r="AQ41" s="315"/>
-      <c r="AR41" s="315"/>
-      <c r="AS41" s="315"/>
-      <c r="AT41" s="316"/>
+      <c r="AO41" s="316"/>
+      <c r="AP41" s="316"/>
+      <c r="AQ41" s="316"/>
+      <c r="AR41" s="316"/>
+      <c r="AS41" s="316"/>
+      <c r="AT41" s="317"/>
       <c r="AU41" s="14"/>
     </row>
     <row r="42" spans="1:47" ht="12.65" customHeight="1" x14ac:dyDescent="0.35">
@@ -6319,22 +6335,22 @@
       <c r="B42" s="27">
         <v>2</v>
       </c>
-      <c r="C42" s="404"/>
-      <c r="D42" s="405"/>
-      <c r="E42" s="405"/>
-      <c r="F42" s="405"/>
-      <c r="G42" s="405"/>
-      <c r="H42" s="406"/>
-      <c r="I42" s="399"/>
+      <c r="C42" s="405"/>
+      <c r="D42" s="406"/>
+      <c r="E42" s="406"/>
+      <c r="F42" s="406"/>
+      <c r="G42" s="406"/>
+      <c r="H42" s="407"/>
+      <c r="I42" s="400"/>
       <c r="J42" s="112"/>
       <c r="K42" s="112"/>
       <c r="L42" s="112"/>
       <c r="M42" s="112"/>
       <c r="N42" s="112"/>
       <c r="O42" s="112"/>
-      <c r="P42" s="400"/>
+      <c r="P42" s="401"/>
       <c r="Q42" s="108" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="R42" s="108"/>
       <c r="S42" s="108"/>
@@ -6343,7 +6359,7 @@
       <c r="V42" s="108"/>
       <c r="W42" s="108"/>
       <c r="X42" s="108" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y42" s="108"/>
       <c r="Z42" s="108"/>
@@ -6395,7 +6411,7 @@
       <c r="O43" s="108"/>
       <c r="P43" s="108"/>
       <c r="Q43" s="108" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R43" s="108"/>
       <c r="S43" s="108"/>
@@ -6404,7 +6420,7 @@
       <c r="V43" s="108"/>
       <c r="W43" s="108"/>
       <c r="X43" s="108" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="Y43" s="108"/>
       <c r="Z43" s="108"/>
@@ -6437,12 +6453,12 @@
       <c r="B44" s="27">
         <v>4</v>
       </c>
-      <c r="C44" s="324"/>
-      <c r="D44" s="325"/>
-      <c r="E44" s="325"/>
-      <c r="F44" s="325"/>
-      <c r="G44" s="325"/>
-      <c r="H44" s="325"/>
+      <c r="C44" s="325"/>
+      <c r="D44" s="326"/>
+      <c r="E44" s="326"/>
+      <c r="F44" s="326"/>
+      <c r="G44" s="326"/>
+      <c r="H44" s="326"/>
       <c r="I44" s="202"/>
       <c r="J44" s="202"/>
       <c r="K44" s="202"/>
@@ -6576,16 +6592,16 @@
       <c r="AM46" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="AN46" s="318">
+      <c r="AN46" s="319">
         <f>SUM(AN41:AT45)</f>
         <v>440128219</v>
       </c>
-      <c r="AO46" s="319"/>
-      <c r="AP46" s="319"/>
-      <c r="AQ46" s="319"/>
-      <c r="AR46" s="319"/>
-      <c r="AS46" s="319"/>
-      <c r="AT46" s="320"/>
+      <c r="AO46" s="320"/>
+      <c r="AP46" s="320"/>
+      <c r="AQ46" s="320"/>
+      <c r="AR46" s="320"/>
+      <c r="AS46" s="320"/>
+      <c r="AT46" s="321"/>
       <c r="AU46" s="14"/>
     </row>
     <row r="47" spans="1:47" ht="12.65" customHeight="1" x14ac:dyDescent="0.35">
@@ -6746,7 +6762,7 @@
       <c r="AQ49" s="206"/>
       <c r="AR49" s="206"/>
       <c r="AS49" s="206"/>
-      <c r="AT49" s="321"/>
+      <c r="AT49" s="322"/>
       <c r="AU49" s="62"/>
     </row>
     <row r="50" spans="1:47" s="63" customFormat="1" ht="12.65" customHeight="1" x14ac:dyDescent="0.35">
@@ -6773,7 +6789,7 @@
       <c r="O50" s="175"/>
       <c r="P50" s="175"/>
       <c r="Q50" s="181" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R50" s="182"/>
       <c r="S50" s="182"/>
@@ -6782,7 +6798,7 @@
       <c r="V50" s="182"/>
       <c r="W50" s="183"/>
       <c r="X50" s="175" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="Y50" s="175"/>
       <c r="Z50" s="175"/>
@@ -6833,17 +6849,17 @@
       <c r="N51" s="216"/>
       <c r="O51" s="216"/>
       <c r="P51" s="216"/>
-      <c r="Q51" s="322" t="s">
-        <v>109</v>
-      </c>
-      <c r="R51" s="323"/>
-      <c r="S51" s="323"/>
-      <c r="T51" s="323"/>
-      <c r="U51" s="323"/>
-      <c r="V51" s="323"/>
+      <c r="Q51" s="323" t="s">
+        <v>107</v>
+      </c>
+      <c r="R51" s="324"/>
+      <c r="S51" s="324"/>
+      <c r="T51" s="324"/>
+      <c r="U51" s="324"/>
+      <c r="V51" s="324"/>
       <c r="W51" s="154"/>
       <c r="X51" s="155" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y51" s="155"/>
       <c r="Z51" s="155"/>
@@ -6876,14 +6892,14 @@
       <c r="B52" s="83">
         <v>3</v>
       </c>
-      <c r="C52" s="330">
+      <c r="C52" s="331">
         <v>46028</v>
       </c>
-      <c r="D52" s="331"/>
-      <c r="E52" s="331"/>
-      <c r="F52" s="331"/>
-      <c r="G52" s="331"/>
-      <c r="H52" s="331"/>
+      <c r="D52" s="332"/>
+      <c r="E52" s="332"/>
+      <c r="F52" s="332"/>
+      <c r="G52" s="332"/>
+      <c r="H52" s="332"/>
       <c r="I52" s="155">
         <v>27706</v>
       </c>
@@ -6895,7 +6911,7 @@
       <c r="O52" s="155"/>
       <c r="P52" s="155"/>
       <c r="Q52" s="155" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R52" s="155"/>
       <c r="S52" s="155"/>
@@ -6904,7 +6920,7 @@
       <c r="V52" s="155"/>
       <c r="W52" s="155"/>
       <c r="X52" s="155" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="Y52" s="155"/>
       <c r="Z52" s="155"/>
@@ -6956,7 +6972,7 @@
       <c r="O53" s="216"/>
       <c r="P53" s="216"/>
       <c r="Q53" s="217" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="R53" s="218"/>
       <c r="S53" s="218"/>
@@ -6965,7 +6981,7 @@
       <c r="V53" s="218"/>
       <c r="W53" s="219"/>
       <c r="X53" s="136" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="Y53" s="136"/>
       <c r="Z53" s="136"/>
@@ -7303,7 +7319,7 @@
       <c r="B60" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="C60" s="326" t="s">
+      <c r="C60" s="327" t="s">
         <v>29</v>
       </c>
       <c r="D60" s="206"/>
@@ -7358,7 +7374,7 @@
       <c r="AQ60" s="206"/>
       <c r="AR60" s="206"/>
       <c r="AS60" s="206"/>
-      <c r="AT60" s="321"/>
+      <c r="AT60" s="322"/>
       <c r="AU60" s="62"/>
     </row>
     <row r="61" spans="1:47" s="63" customFormat="1" ht="12.65" customHeight="1" x14ac:dyDescent="0.35">
@@ -7366,8 +7382,8 @@
       <c r="B61" s="90">
         <v>1</v>
       </c>
-      <c r="C61" s="329" t="s">
-        <v>113</v>
+      <c r="C61" s="330" t="s">
+        <v>111</v>
       </c>
       <c r="D61" s="175"/>
       <c r="E61" s="175"/>
@@ -7375,30 +7391,30 @@
       <c r="G61" s="175"/>
       <c r="H61" s="175"/>
       <c r="I61" s="175" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="J61" s="175"/>
       <c r="K61" s="175"/>
       <c r="L61" s="175"/>
       <c r="M61" s="175"/>
-      <c r="N61" s="332" t="s">
-        <v>105</v>
-      </c>
-      <c r="O61" s="333"/>
-      <c r="P61" s="333"/>
-      <c r="Q61" s="333"/>
-      <c r="R61" s="333"/>
-      <c r="S61" s="333"/>
-      <c r="T61" s="333"/>
-      <c r="U61" s="333"/>
-      <c r="V61" s="333"/>
-      <c r="W61" s="333"/>
-      <c r="X61" s="333"/>
-      <c r="Y61" s="333"/>
-      <c r="Z61" s="333"/>
-      <c r="AA61" s="333"/>
-      <c r="AB61" s="333"/>
-      <c r="AC61" s="334"/>
+      <c r="N61" s="333" t="s">
+        <v>103</v>
+      </c>
+      <c r="O61" s="334"/>
+      <c r="P61" s="334"/>
+      <c r="Q61" s="334"/>
+      <c r="R61" s="334"/>
+      <c r="S61" s="334"/>
+      <c r="T61" s="334"/>
+      <c r="U61" s="334"/>
+      <c r="V61" s="334"/>
+      <c r="W61" s="334"/>
+      <c r="X61" s="334"/>
+      <c r="Y61" s="334"/>
+      <c r="Z61" s="334"/>
+      <c r="AA61" s="334"/>
+      <c r="AB61" s="334"/>
+      <c r="AC61" s="335"/>
       <c r="AD61" s="178">
         <v>45957</v>
       </c>
@@ -7440,8 +7456,8 @@
       <c r="K62" s="175"/>
       <c r="L62" s="175"/>
       <c r="M62" s="175"/>
-      <c r="N62" s="328" t="s">
-        <v>111</v>
+      <c r="N62" s="329" t="s">
+        <v>109</v>
       </c>
       <c r="O62" s="172"/>
       <c r="P62" s="172"/>
@@ -7499,8 +7515,8 @@
       <c r="K63" s="175"/>
       <c r="L63" s="175"/>
       <c r="M63" s="175"/>
-      <c r="N63" s="328" t="s">
-        <v>112</v>
+      <c r="N63" s="329" t="s">
+        <v>110</v>
       </c>
       <c r="O63" s="172"/>
       <c r="P63" s="172"/>
@@ -7574,16 +7590,16 @@
       <c r="AA64" s="172"/>
       <c r="AB64" s="172"/>
       <c r="AC64" s="173"/>
-      <c r="AD64" s="327"/>
-      <c r="AE64" s="327"/>
-      <c r="AF64" s="327"/>
-      <c r="AG64" s="327"/>
-      <c r="AH64" s="327"/>
-      <c r="AI64" s="327"/>
-      <c r="AJ64" s="327"/>
-      <c r="AK64" s="327"/>
-      <c r="AL64" s="327"/>
-      <c r="AM64" s="327"/>
+      <c r="AD64" s="328"/>
+      <c r="AE64" s="328"/>
+      <c r="AF64" s="328"/>
+      <c r="AG64" s="328"/>
+      <c r="AH64" s="328"/>
+      <c r="AI64" s="328"/>
+      <c r="AJ64" s="328"/>
+      <c r="AK64" s="328"/>
+      <c r="AL64" s="328"/>
+      <c r="AM64" s="328"/>
       <c r="AN64" s="187"/>
       <c r="AO64" s="188"/>
       <c r="AP64" s="188"/>
@@ -7844,7 +7860,7 @@
     </row>
     <row r="70" spans="1:47" ht="63" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="13"/>
-      <c r="B70" s="344" t="s">
+      <c r="B70" s="345" t="s">
         <v>3</v>
       </c>
       <c r="C70" s="163"/>
@@ -7867,7 +7883,7 @@
       <c r="R70" s="163"/>
       <c r="S70" s="163"/>
       <c r="T70" s="163"/>
-      <c r="U70" s="346"/>
+      <c r="U70" s="347"/>
       <c r="V70" s="159" t="s">
         <v>86</v>
       </c>
@@ -7909,26 +7925,26 @@
     </row>
     <row r="71" spans="1:47" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="13"/>
-      <c r="B71" s="345"/>
+      <c r="B71" s="346"/>
       <c r="C71" s="166"/>
       <c r="D71" s="166"/>
       <c r="E71" s="166"/>
-      <c r="F71" s="347"/>
-      <c r="G71" s="348"/>
-      <c r="H71" s="348"/>
-      <c r="I71" s="348"/>
-      <c r="J71" s="348"/>
-      <c r="K71" s="348"/>
-      <c r="L71" s="348"/>
-      <c r="M71" s="348"/>
-      <c r="N71" s="348"/>
-      <c r="O71" s="348"/>
-      <c r="P71" s="348"/>
-      <c r="Q71" s="348"/>
-      <c r="R71" s="348"/>
-      <c r="S71" s="348"/>
-      <c r="T71" s="348"/>
-      <c r="U71" s="349"/>
+      <c r="F71" s="348"/>
+      <c r="G71" s="349"/>
+      <c r="H71" s="349"/>
+      <c r="I71" s="349"/>
+      <c r="J71" s="349"/>
+      <c r="K71" s="349"/>
+      <c r="L71" s="349"/>
+      <c r="M71" s="349"/>
+      <c r="N71" s="349"/>
+      <c r="O71" s="349"/>
+      <c r="P71" s="349"/>
+      <c r="Q71" s="349"/>
+      <c r="R71" s="349"/>
+      <c r="S71" s="349"/>
+      <c r="T71" s="349"/>
+      <c r="U71" s="350"/>
       <c r="V71" s="161"/>
       <c r="W71" s="161"/>
       <c r="X71" s="161"/>
@@ -7965,7 +7981,7 @@
       <c r="D72" s="150"/>
       <c r="E72" s="151"/>
       <c r="F72" s="152" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G72" s="152"/>
       <c r="H72" s="152"/>
@@ -7990,25 +8006,25 @@
       <c r="AA72" s="153"/>
       <c r="AB72" s="153"/>
       <c r="AC72" s="153"/>
-      <c r="AD72" s="354" t="s">
-        <v>135</v>
-      </c>
-      <c r="AE72" s="355"/>
-      <c r="AF72" s="356"/>
-      <c r="AG72" s="354"/>
-      <c r="AH72" s="355"/>
-      <c r="AI72" s="356"/>
-      <c r="AJ72" s="357"/>
-      <c r="AK72" s="358"/>
-      <c r="AL72" s="358"/>
-      <c r="AM72" s="358"/>
-      <c r="AN72" s="358"/>
-      <c r="AO72" s="358"/>
-      <c r="AP72" s="358"/>
-      <c r="AQ72" s="358"/>
-      <c r="AR72" s="358"/>
-      <c r="AS72" s="358"/>
-      <c r="AT72" s="359"/>
+      <c r="AD72" s="355" t="s">
+        <v>133</v>
+      </c>
+      <c r="AE72" s="356"/>
+      <c r="AF72" s="357"/>
+      <c r="AG72" s="355"/>
+      <c r="AH72" s="356"/>
+      <c r="AI72" s="357"/>
+      <c r="AJ72" s="358"/>
+      <c r="AK72" s="359"/>
+      <c r="AL72" s="359"/>
+      <c r="AM72" s="359"/>
+      <c r="AN72" s="359"/>
+      <c r="AO72" s="359"/>
+      <c r="AP72" s="359"/>
+      <c r="AQ72" s="359"/>
+      <c r="AR72" s="359"/>
+      <c r="AS72" s="359"/>
+      <c r="AT72" s="360"/>
       <c r="AU72" s="14"/>
     </row>
     <row r="73" spans="1:47" ht="189" customHeight="1" x14ac:dyDescent="0.35">
@@ -8020,7 +8036,7 @@
       <c r="D73" s="150"/>
       <c r="E73" s="151"/>
       <c r="F73" s="152" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G73" s="152"/>
       <c r="H73" s="152"/>
@@ -8045,25 +8061,25 @@
       <c r="AA73" s="153"/>
       <c r="AB73" s="153"/>
       <c r="AC73" s="153"/>
-      <c r="AD73" s="354" t="s">
-        <v>135</v>
-      </c>
-      <c r="AE73" s="355"/>
-      <c r="AF73" s="356"/>
-      <c r="AG73" s="354"/>
-      <c r="AH73" s="355"/>
-      <c r="AI73" s="356"/>
-      <c r="AJ73" s="357"/>
-      <c r="AK73" s="358"/>
-      <c r="AL73" s="358"/>
-      <c r="AM73" s="358"/>
-      <c r="AN73" s="358"/>
-      <c r="AO73" s="358"/>
-      <c r="AP73" s="358"/>
-      <c r="AQ73" s="358"/>
-      <c r="AR73" s="358"/>
-      <c r="AS73" s="358"/>
-      <c r="AT73" s="359"/>
+      <c r="AD73" s="355" t="s">
+        <v>133</v>
+      </c>
+      <c r="AE73" s="356"/>
+      <c r="AF73" s="357"/>
+      <c r="AG73" s="355"/>
+      <c r="AH73" s="356"/>
+      <c r="AI73" s="357"/>
+      <c r="AJ73" s="358"/>
+      <c r="AK73" s="359"/>
+      <c r="AL73" s="359"/>
+      <c r="AM73" s="359"/>
+      <c r="AN73" s="359"/>
+      <c r="AO73" s="359"/>
+      <c r="AP73" s="359"/>
+      <c r="AQ73" s="359"/>
+      <c r="AR73" s="359"/>
+      <c r="AS73" s="359"/>
+      <c r="AT73" s="360"/>
       <c r="AU73" s="14"/>
     </row>
     <row r="74" spans="1:47" ht="157" customHeight="1" x14ac:dyDescent="0.35">
@@ -8075,7 +8091,7 @@
       <c r="D74" s="150"/>
       <c r="E74" s="151"/>
       <c r="F74" s="152" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G74" s="152"/>
       <c r="H74" s="152"/>
@@ -8093,7 +8109,7 @@
       <c r="T74" s="152"/>
       <c r="U74" s="152"/>
       <c r="V74" s="153" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="W74" s="153"/>
       <c r="X74" s="153"/>
@@ -8102,25 +8118,25 @@
       <c r="AA74" s="153"/>
       <c r="AB74" s="153"/>
       <c r="AC74" s="153"/>
-      <c r="AD74" s="354"/>
-      <c r="AE74" s="355"/>
-      <c r="AF74" s="356"/>
-      <c r="AG74" s="354"/>
-      <c r="AH74" s="355"/>
-      <c r="AI74" s="356"/>
-      <c r="AJ74" s="360" t="s">
-        <v>136</v>
-      </c>
-      <c r="AK74" s="361"/>
-      <c r="AL74" s="361"/>
-      <c r="AM74" s="361"/>
-      <c r="AN74" s="361"/>
-      <c r="AO74" s="361"/>
-      <c r="AP74" s="361"/>
-      <c r="AQ74" s="361"/>
-      <c r="AR74" s="361"/>
-      <c r="AS74" s="361"/>
-      <c r="AT74" s="362"/>
+      <c r="AD74" s="355"/>
+      <c r="AE74" s="356"/>
+      <c r="AF74" s="357"/>
+      <c r="AG74" s="355"/>
+      <c r="AH74" s="356"/>
+      <c r="AI74" s="357"/>
+      <c r="AJ74" s="361" t="s">
+        <v>134</v>
+      </c>
+      <c r="AK74" s="362"/>
+      <c r="AL74" s="362"/>
+      <c r="AM74" s="362"/>
+      <c r="AN74" s="362"/>
+      <c r="AO74" s="362"/>
+      <c r="AP74" s="362"/>
+      <c r="AQ74" s="362"/>
+      <c r="AR74" s="362"/>
+      <c r="AS74" s="362"/>
+      <c r="AT74" s="363"/>
       <c r="AU74" s="14"/>
     </row>
     <row r="75" spans="1:47" ht="196.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -8132,7 +8148,7 @@
       <c r="D75" s="150"/>
       <c r="E75" s="151"/>
       <c r="F75" s="152" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G75" s="152"/>
       <c r="H75" s="152"/>
@@ -8150,7 +8166,7 @@
       <c r="T75" s="152"/>
       <c r="U75" s="152"/>
       <c r="V75" s="153" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="W75" s="153"/>
       <c r="X75" s="153"/>
@@ -8159,25 +8175,25 @@
       <c r="AA75" s="153"/>
       <c r="AB75" s="153"/>
       <c r="AC75" s="153"/>
-      <c r="AD75" s="354"/>
-      <c r="AE75" s="355"/>
-      <c r="AF75" s="356"/>
-      <c r="AG75" s="354"/>
-      <c r="AH75" s="355"/>
-      <c r="AI75" s="356"/>
-      <c r="AJ75" s="360" t="s">
-        <v>137</v>
-      </c>
-      <c r="AK75" s="361"/>
-      <c r="AL75" s="361"/>
-      <c r="AM75" s="361"/>
-      <c r="AN75" s="361"/>
-      <c r="AO75" s="361"/>
-      <c r="AP75" s="361"/>
-      <c r="AQ75" s="361"/>
-      <c r="AR75" s="361"/>
-      <c r="AS75" s="361"/>
-      <c r="AT75" s="362"/>
+      <c r="AD75" s="355"/>
+      <c r="AE75" s="356"/>
+      <c r="AF75" s="357"/>
+      <c r="AG75" s="355"/>
+      <c r="AH75" s="356"/>
+      <c r="AI75" s="357"/>
+      <c r="AJ75" s="361" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK75" s="362"/>
+      <c r="AL75" s="362"/>
+      <c r="AM75" s="362"/>
+      <c r="AN75" s="362"/>
+      <c r="AO75" s="362"/>
+      <c r="AP75" s="362"/>
+      <c r="AQ75" s="362"/>
+      <c r="AR75" s="362"/>
+      <c r="AS75" s="362"/>
+      <c r="AT75" s="363"/>
       <c r="AU75" s="14"/>
     </row>
     <row r="76" spans="1:47" ht="41" customHeight="1" x14ac:dyDescent="0.35">
@@ -8189,7 +8205,7 @@
       <c r="D76" s="150"/>
       <c r="E76" s="151"/>
       <c r="F76" s="152" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G76" s="152"/>
       <c r="H76" s="152"/>
@@ -8214,25 +8230,25 @@
       <c r="AA76" s="153"/>
       <c r="AB76" s="153"/>
       <c r="AC76" s="153"/>
-      <c r="AD76" s="354" t="s">
-        <v>135</v>
-      </c>
-      <c r="AE76" s="355"/>
-      <c r="AF76" s="356"/>
-      <c r="AG76" s="354"/>
-      <c r="AH76" s="355"/>
-      <c r="AI76" s="356"/>
-      <c r="AJ76" s="357"/>
-      <c r="AK76" s="358"/>
-      <c r="AL76" s="358"/>
-      <c r="AM76" s="358"/>
-      <c r="AN76" s="358"/>
-      <c r="AO76" s="358"/>
-      <c r="AP76" s="358"/>
-      <c r="AQ76" s="358"/>
-      <c r="AR76" s="358"/>
-      <c r="AS76" s="358"/>
-      <c r="AT76" s="359"/>
+      <c r="AD76" s="355" t="s">
+        <v>133</v>
+      </c>
+      <c r="AE76" s="356"/>
+      <c r="AF76" s="357"/>
+      <c r="AG76" s="355"/>
+      <c r="AH76" s="356"/>
+      <c r="AI76" s="357"/>
+      <c r="AJ76" s="358"/>
+      <c r="AK76" s="359"/>
+      <c r="AL76" s="359"/>
+      <c r="AM76" s="359"/>
+      <c r="AN76" s="359"/>
+      <c r="AO76" s="359"/>
+      <c r="AP76" s="359"/>
+      <c r="AQ76" s="359"/>
+      <c r="AR76" s="359"/>
+      <c r="AS76" s="359"/>
+      <c r="AT76" s="360"/>
       <c r="AU76" s="14"/>
     </row>
     <row r="77" spans="1:47" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -8244,7 +8260,7 @@
       <c r="D77" s="150"/>
       <c r="E77" s="151"/>
       <c r="F77" s="152" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G77" s="152"/>
       <c r="H77" s="152"/>
@@ -8262,7 +8278,7 @@
       <c r="T77" s="152"/>
       <c r="U77" s="152"/>
       <c r="V77" s="153" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="W77" s="153"/>
       <c r="X77" s="153"/>
@@ -8271,25 +8287,25 @@
       <c r="AA77" s="153"/>
       <c r="AB77" s="153"/>
       <c r="AC77" s="153"/>
-      <c r="AD77" s="354"/>
-      <c r="AE77" s="355"/>
-      <c r="AF77" s="356"/>
-      <c r="AG77" s="354"/>
-      <c r="AH77" s="355"/>
-      <c r="AI77" s="356"/>
-      <c r="AJ77" s="360" t="s">
-        <v>137</v>
-      </c>
-      <c r="AK77" s="361"/>
-      <c r="AL77" s="361"/>
-      <c r="AM77" s="361"/>
-      <c r="AN77" s="361"/>
-      <c r="AO77" s="361"/>
-      <c r="AP77" s="361"/>
-      <c r="AQ77" s="361"/>
-      <c r="AR77" s="361"/>
-      <c r="AS77" s="361"/>
-      <c r="AT77" s="362"/>
+      <c r="AD77" s="355"/>
+      <c r="AE77" s="356"/>
+      <c r="AF77" s="357"/>
+      <c r="AG77" s="355"/>
+      <c r="AH77" s="356"/>
+      <c r="AI77" s="357"/>
+      <c r="AJ77" s="361" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK77" s="362"/>
+      <c r="AL77" s="362"/>
+      <c r="AM77" s="362"/>
+      <c r="AN77" s="362"/>
+      <c r="AO77" s="362"/>
+      <c r="AP77" s="362"/>
+      <c r="AQ77" s="362"/>
+      <c r="AR77" s="362"/>
+      <c r="AS77" s="362"/>
+      <c r="AT77" s="363"/>
       <c r="AU77" s="14"/>
     </row>
     <row r="78" spans="1:47" ht="27" customHeight="1" x14ac:dyDescent="0.35">
@@ -8301,7 +8317,7 @@
       <c r="D78" s="150"/>
       <c r="E78" s="151"/>
       <c r="F78" s="152" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G78" s="152"/>
       <c r="H78" s="152"/>
@@ -8319,7 +8335,7 @@
       <c r="T78" s="152"/>
       <c r="U78" s="152"/>
       <c r="V78" s="153" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="W78" s="153"/>
       <c r="X78" s="153"/>
@@ -8328,25 +8344,25 @@
       <c r="AA78" s="153"/>
       <c r="AB78" s="153"/>
       <c r="AC78" s="153"/>
-      <c r="AD78" s="354"/>
-      <c r="AE78" s="355"/>
-      <c r="AF78" s="356"/>
-      <c r="AG78" s="354"/>
-      <c r="AH78" s="355"/>
-      <c r="AI78" s="356"/>
-      <c r="AJ78" s="360" t="s">
-        <v>137</v>
-      </c>
-      <c r="AK78" s="361"/>
-      <c r="AL78" s="361"/>
-      <c r="AM78" s="361"/>
-      <c r="AN78" s="361"/>
-      <c r="AO78" s="361"/>
-      <c r="AP78" s="361"/>
-      <c r="AQ78" s="361"/>
-      <c r="AR78" s="361"/>
-      <c r="AS78" s="361"/>
-      <c r="AT78" s="362"/>
+      <c r="AD78" s="355"/>
+      <c r="AE78" s="356"/>
+      <c r="AF78" s="357"/>
+      <c r="AG78" s="355"/>
+      <c r="AH78" s="356"/>
+      <c r="AI78" s="357"/>
+      <c r="AJ78" s="361" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK78" s="362"/>
+      <c r="AL78" s="362"/>
+      <c r="AM78" s="362"/>
+      <c r="AN78" s="362"/>
+      <c r="AO78" s="362"/>
+      <c r="AP78" s="362"/>
+      <c r="AQ78" s="362"/>
+      <c r="AR78" s="362"/>
+      <c r="AS78" s="362"/>
+      <c r="AT78" s="363"/>
       <c r="AU78" s="14"/>
     </row>
     <row r="79" spans="1:47" ht="22" customHeight="1" x14ac:dyDescent="0.35">
@@ -8358,7 +8374,7 @@
       <c r="D79" s="150"/>
       <c r="E79" s="151"/>
       <c r="F79" s="152" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G79" s="152"/>
       <c r="H79" s="152"/>
@@ -8383,25 +8399,25 @@
       <c r="AA79" s="153"/>
       <c r="AB79" s="153"/>
       <c r="AC79" s="153"/>
-      <c r="AD79" s="354" t="s">
-        <v>135</v>
-      </c>
-      <c r="AE79" s="355"/>
-      <c r="AF79" s="356"/>
-      <c r="AG79" s="354"/>
-      <c r="AH79" s="355"/>
-      <c r="AI79" s="356"/>
-      <c r="AJ79" s="357"/>
-      <c r="AK79" s="358"/>
-      <c r="AL79" s="358"/>
-      <c r="AM79" s="358"/>
-      <c r="AN79" s="358"/>
-      <c r="AO79" s="358"/>
-      <c r="AP79" s="358"/>
-      <c r="AQ79" s="358"/>
-      <c r="AR79" s="358"/>
-      <c r="AS79" s="358"/>
-      <c r="AT79" s="359"/>
+      <c r="AD79" s="355" t="s">
+        <v>133</v>
+      </c>
+      <c r="AE79" s="356"/>
+      <c r="AF79" s="357"/>
+      <c r="AG79" s="355"/>
+      <c r="AH79" s="356"/>
+      <c r="AI79" s="357"/>
+      <c r="AJ79" s="358"/>
+      <c r="AK79" s="359"/>
+      <c r="AL79" s="359"/>
+      <c r="AM79" s="359"/>
+      <c r="AN79" s="359"/>
+      <c r="AO79" s="359"/>
+      <c r="AP79" s="359"/>
+      <c r="AQ79" s="359"/>
+      <c r="AR79" s="359"/>
+      <c r="AS79" s="359"/>
+      <c r="AT79" s="360"/>
       <c r="AU79" s="14"/>
     </row>
     <row r="80" spans="1:47" ht="38" customHeight="1" x14ac:dyDescent="0.35">
@@ -8413,7 +8429,7 @@
       <c r="D80" s="150"/>
       <c r="E80" s="151"/>
       <c r="F80" s="152" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G80" s="152"/>
       <c r="H80" s="152"/>
@@ -8436,29 +8452,29 @@
       <c r="Y80" s="153"/>
       <c r="Z80" s="153"/>
       <c r="AA80" s="153" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AB80" s="153"/>
       <c r="AC80" s="153"/>
-      <c r="AD80" s="354"/>
-      <c r="AE80" s="355"/>
-      <c r="AF80" s="356"/>
-      <c r="AG80" s="354"/>
-      <c r="AH80" s="355"/>
-      <c r="AI80" s="356"/>
-      <c r="AJ80" s="360" t="s">
-        <v>137</v>
-      </c>
-      <c r="AK80" s="361"/>
-      <c r="AL80" s="361"/>
-      <c r="AM80" s="361"/>
-      <c r="AN80" s="361"/>
-      <c r="AO80" s="361"/>
-      <c r="AP80" s="361"/>
-      <c r="AQ80" s="361"/>
-      <c r="AR80" s="361"/>
-      <c r="AS80" s="361"/>
-      <c r="AT80" s="362"/>
+      <c r="AD80" s="355"/>
+      <c r="AE80" s="356"/>
+      <c r="AF80" s="357"/>
+      <c r="AG80" s="355"/>
+      <c r="AH80" s="356"/>
+      <c r="AI80" s="357"/>
+      <c r="AJ80" s="361" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK80" s="362"/>
+      <c r="AL80" s="362"/>
+      <c r="AM80" s="362"/>
+      <c r="AN80" s="362"/>
+      <c r="AO80" s="362"/>
+      <c r="AP80" s="362"/>
+      <c r="AQ80" s="362"/>
+      <c r="AR80" s="362"/>
+      <c r="AS80" s="362"/>
+      <c r="AT80" s="363"/>
       <c r="AU80" s="14"/>
     </row>
     <row r="81" spans="1:47" ht="26" customHeight="1" x14ac:dyDescent="0.35">
@@ -8470,7 +8486,7 @@
       <c r="D81" s="150"/>
       <c r="E81" s="151"/>
       <c r="F81" s="152" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G81" s="152"/>
       <c r="H81" s="152"/>
@@ -8493,29 +8509,29 @@
       <c r="Y81" s="153"/>
       <c r="Z81" s="153"/>
       <c r="AA81" s="153" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AB81" s="153"/>
       <c r="AC81" s="153"/>
-      <c r="AD81" s="354"/>
-      <c r="AE81" s="355"/>
-      <c r="AF81" s="356"/>
-      <c r="AG81" s="354"/>
-      <c r="AH81" s="355"/>
-      <c r="AI81" s="356"/>
-      <c r="AJ81" s="360" t="s">
-        <v>137</v>
-      </c>
-      <c r="AK81" s="361"/>
-      <c r="AL81" s="361"/>
-      <c r="AM81" s="361"/>
-      <c r="AN81" s="361"/>
-      <c r="AO81" s="361"/>
-      <c r="AP81" s="361"/>
-      <c r="AQ81" s="361"/>
-      <c r="AR81" s="361"/>
-      <c r="AS81" s="361"/>
-      <c r="AT81" s="362"/>
+      <c r="AD81" s="355"/>
+      <c r="AE81" s="356"/>
+      <c r="AF81" s="357"/>
+      <c r="AG81" s="355"/>
+      <c r="AH81" s="356"/>
+      <c r="AI81" s="357"/>
+      <c r="AJ81" s="361" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK81" s="362"/>
+      <c r="AL81" s="362"/>
+      <c r="AM81" s="362"/>
+      <c r="AN81" s="362"/>
+      <c r="AO81" s="362"/>
+      <c r="AP81" s="362"/>
+      <c r="AQ81" s="362"/>
+      <c r="AR81" s="362"/>
+      <c r="AS81" s="362"/>
+      <c r="AT81" s="363"/>
       <c r="AU81" s="14"/>
     </row>
     <row r="82" spans="1:47" ht="41.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -8527,7 +8543,7 @@
       <c r="D82" s="150"/>
       <c r="E82" s="151"/>
       <c r="F82" s="152" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G82" s="152"/>
       <c r="H82" s="152"/>
@@ -8550,29 +8566,29 @@
       <c r="Y82" s="153"/>
       <c r="Z82" s="153"/>
       <c r="AA82" s="153" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AB82" s="153"/>
       <c r="AC82" s="153"/>
-      <c r="AD82" s="354"/>
-      <c r="AE82" s="355"/>
-      <c r="AF82" s="356"/>
-      <c r="AG82" s="354"/>
-      <c r="AH82" s="355"/>
-      <c r="AI82" s="356"/>
-      <c r="AJ82" s="360" t="s">
-        <v>137</v>
-      </c>
-      <c r="AK82" s="361"/>
-      <c r="AL82" s="361"/>
-      <c r="AM82" s="361"/>
-      <c r="AN82" s="361"/>
-      <c r="AO82" s="361"/>
-      <c r="AP82" s="361"/>
-      <c r="AQ82" s="361"/>
-      <c r="AR82" s="361"/>
-      <c r="AS82" s="361"/>
-      <c r="AT82" s="362"/>
+      <c r="AD82" s="355"/>
+      <c r="AE82" s="356"/>
+      <c r="AF82" s="357"/>
+      <c r="AG82" s="355"/>
+      <c r="AH82" s="356"/>
+      <c r="AI82" s="357"/>
+      <c r="AJ82" s="361" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK82" s="362"/>
+      <c r="AL82" s="362"/>
+      <c r="AM82" s="362"/>
+      <c r="AN82" s="362"/>
+      <c r="AO82" s="362"/>
+      <c r="AP82" s="362"/>
+      <c r="AQ82" s="362"/>
+      <c r="AR82" s="362"/>
+      <c r="AS82" s="362"/>
+      <c r="AT82" s="363"/>
       <c r="AU82" s="14"/>
     </row>
     <row r="83" spans="1:47" ht="27" customHeight="1" x14ac:dyDescent="0.35">
@@ -8584,7 +8600,7 @@
       <c r="D83" s="150"/>
       <c r="E83" s="151"/>
       <c r="F83" s="152" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G83" s="152"/>
       <c r="H83" s="152"/>
@@ -8609,25 +8625,25 @@
       <c r="AA83" s="153"/>
       <c r="AB83" s="153"/>
       <c r="AC83" s="153"/>
-      <c r="AD83" s="354" t="s">
-        <v>135</v>
-      </c>
-      <c r="AE83" s="355"/>
-      <c r="AF83" s="356"/>
-      <c r="AG83" s="354"/>
-      <c r="AH83" s="355"/>
-      <c r="AI83" s="356"/>
-      <c r="AJ83" s="357"/>
-      <c r="AK83" s="358"/>
-      <c r="AL83" s="358"/>
-      <c r="AM83" s="358"/>
-      <c r="AN83" s="358"/>
-      <c r="AO83" s="358"/>
-      <c r="AP83" s="358"/>
-      <c r="AQ83" s="358"/>
-      <c r="AR83" s="358"/>
-      <c r="AS83" s="358"/>
-      <c r="AT83" s="359"/>
+      <c r="AD83" s="355" t="s">
+        <v>133</v>
+      </c>
+      <c r="AE83" s="356"/>
+      <c r="AF83" s="357"/>
+      <c r="AG83" s="355"/>
+      <c r="AH83" s="356"/>
+      <c r="AI83" s="357"/>
+      <c r="AJ83" s="358"/>
+      <c r="AK83" s="359"/>
+      <c r="AL83" s="359"/>
+      <c r="AM83" s="359"/>
+      <c r="AN83" s="359"/>
+      <c r="AO83" s="359"/>
+      <c r="AP83" s="359"/>
+      <c r="AQ83" s="359"/>
+      <c r="AR83" s="359"/>
+      <c r="AS83" s="359"/>
+      <c r="AT83" s="360"/>
       <c r="AU83" s="14"/>
     </row>
     <row r="84" spans="1:47" ht="27" customHeight="1" x14ac:dyDescent="0.35">
@@ -8639,7 +8655,7 @@
       <c r="D84" s="150"/>
       <c r="E84" s="151"/>
       <c r="F84" s="152" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G84" s="152"/>
       <c r="H84" s="152"/>
@@ -8664,25 +8680,25 @@
       <c r="AA84" s="153"/>
       <c r="AB84" s="153"/>
       <c r="AC84" s="153"/>
-      <c r="AD84" s="354" t="s">
-        <v>135</v>
-      </c>
-      <c r="AE84" s="355"/>
-      <c r="AF84" s="356"/>
-      <c r="AG84" s="354"/>
-      <c r="AH84" s="355"/>
-      <c r="AI84" s="356"/>
-      <c r="AJ84" s="357"/>
-      <c r="AK84" s="358"/>
-      <c r="AL84" s="358"/>
-      <c r="AM84" s="358"/>
-      <c r="AN84" s="358"/>
-      <c r="AO84" s="358"/>
-      <c r="AP84" s="358"/>
-      <c r="AQ84" s="358"/>
-      <c r="AR84" s="358"/>
-      <c r="AS84" s="358"/>
-      <c r="AT84" s="359"/>
+      <c r="AD84" s="355" t="s">
+        <v>133</v>
+      </c>
+      <c r="AE84" s="356"/>
+      <c r="AF84" s="357"/>
+      <c r="AG84" s="355"/>
+      <c r="AH84" s="356"/>
+      <c r="AI84" s="357"/>
+      <c r="AJ84" s="358"/>
+      <c r="AK84" s="359"/>
+      <c r="AL84" s="359"/>
+      <c r="AM84" s="359"/>
+      <c r="AN84" s="359"/>
+      <c r="AO84" s="359"/>
+      <c r="AP84" s="359"/>
+      <c r="AQ84" s="359"/>
+      <c r="AR84" s="359"/>
+      <c r="AS84" s="359"/>
+      <c r="AT84" s="360"/>
       <c r="AU84" s="14"/>
     </row>
     <row r="85" spans="1:47" ht="45.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -8694,7 +8710,7 @@
       <c r="D85" s="150"/>
       <c r="E85" s="151"/>
       <c r="F85" s="152" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G85" s="152"/>
       <c r="H85" s="152"/>
@@ -8719,25 +8735,25 @@
       <c r="AA85" s="153"/>
       <c r="AB85" s="153"/>
       <c r="AC85" s="153"/>
-      <c r="AD85" s="354" t="s">
-        <v>135</v>
-      </c>
-      <c r="AE85" s="355"/>
-      <c r="AF85" s="356"/>
-      <c r="AG85" s="354"/>
-      <c r="AH85" s="355"/>
-      <c r="AI85" s="356"/>
-      <c r="AJ85" s="357"/>
-      <c r="AK85" s="358"/>
-      <c r="AL85" s="358"/>
-      <c r="AM85" s="358"/>
-      <c r="AN85" s="358"/>
-      <c r="AO85" s="358"/>
-      <c r="AP85" s="358"/>
-      <c r="AQ85" s="358"/>
-      <c r="AR85" s="358"/>
-      <c r="AS85" s="358"/>
-      <c r="AT85" s="359"/>
+      <c r="AD85" s="355" t="s">
+        <v>133</v>
+      </c>
+      <c r="AE85" s="356"/>
+      <c r="AF85" s="357"/>
+      <c r="AG85" s="355"/>
+      <c r="AH85" s="356"/>
+      <c r="AI85" s="357"/>
+      <c r="AJ85" s="358"/>
+      <c r="AK85" s="359"/>
+      <c r="AL85" s="359"/>
+      <c r="AM85" s="359"/>
+      <c r="AN85" s="359"/>
+      <c r="AO85" s="359"/>
+      <c r="AP85" s="359"/>
+      <c r="AQ85" s="359"/>
+      <c r="AR85" s="359"/>
+      <c r="AS85" s="359"/>
+      <c r="AT85" s="360"/>
       <c r="AU85" s="14"/>
     </row>
     <row r="86" spans="1:47" ht="27" customHeight="1" x14ac:dyDescent="0.35">
@@ -8749,7 +8765,7 @@
       <c r="D86" s="150"/>
       <c r="E86" s="151"/>
       <c r="F86" s="152" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G86" s="152"/>
       <c r="H86" s="152"/>
@@ -8774,25 +8790,25 @@
       <c r="AA86" s="153"/>
       <c r="AB86" s="153"/>
       <c r="AC86" s="153"/>
-      <c r="AD86" s="354" t="s">
-        <v>135</v>
-      </c>
-      <c r="AE86" s="355"/>
-      <c r="AF86" s="356"/>
-      <c r="AG86" s="354"/>
-      <c r="AH86" s="355"/>
-      <c r="AI86" s="356"/>
-      <c r="AJ86" s="357"/>
-      <c r="AK86" s="358"/>
-      <c r="AL86" s="358"/>
-      <c r="AM86" s="358"/>
-      <c r="AN86" s="358"/>
-      <c r="AO86" s="358"/>
-      <c r="AP86" s="358"/>
-      <c r="AQ86" s="358"/>
-      <c r="AR86" s="358"/>
-      <c r="AS86" s="358"/>
-      <c r="AT86" s="359"/>
+      <c r="AD86" s="355" t="s">
+        <v>133</v>
+      </c>
+      <c r="AE86" s="356"/>
+      <c r="AF86" s="357"/>
+      <c r="AG86" s="355"/>
+      <c r="AH86" s="356"/>
+      <c r="AI86" s="357"/>
+      <c r="AJ86" s="358"/>
+      <c r="AK86" s="359"/>
+      <c r="AL86" s="359"/>
+      <c r="AM86" s="359"/>
+      <c r="AN86" s="359"/>
+      <c r="AO86" s="359"/>
+      <c r="AP86" s="359"/>
+      <c r="AQ86" s="359"/>
+      <c r="AR86" s="359"/>
+      <c r="AS86" s="359"/>
+      <c r="AT86" s="360"/>
       <c r="AU86" s="14"/>
     </row>
     <row r="87" spans="1:47" ht="27" customHeight="1" x14ac:dyDescent="0.35">
@@ -8804,7 +8820,7 @@
       <c r="D87" s="150"/>
       <c r="E87" s="151"/>
       <c r="F87" s="152" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G87" s="152"/>
       <c r="H87" s="152"/>
@@ -8829,25 +8845,25 @@
       <c r="AA87" s="153"/>
       <c r="AB87" s="153"/>
       <c r="AC87" s="153"/>
-      <c r="AD87" s="354" t="s">
-        <v>135</v>
-      </c>
-      <c r="AE87" s="355"/>
-      <c r="AF87" s="356"/>
-      <c r="AG87" s="354"/>
-      <c r="AH87" s="355"/>
-      <c r="AI87" s="356"/>
-      <c r="AJ87" s="357"/>
-      <c r="AK87" s="358"/>
-      <c r="AL87" s="358"/>
-      <c r="AM87" s="358"/>
-      <c r="AN87" s="358"/>
-      <c r="AO87" s="358"/>
-      <c r="AP87" s="358"/>
-      <c r="AQ87" s="358"/>
-      <c r="AR87" s="358"/>
-      <c r="AS87" s="358"/>
-      <c r="AT87" s="359"/>
+      <c r="AD87" s="355" t="s">
+        <v>133</v>
+      </c>
+      <c r="AE87" s="356"/>
+      <c r="AF87" s="357"/>
+      <c r="AG87" s="355"/>
+      <c r="AH87" s="356"/>
+      <c r="AI87" s="357"/>
+      <c r="AJ87" s="358"/>
+      <c r="AK87" s="359"/>
+      <c r="AL87" s="359"/>
+      <c r="AM87" s="359"/>
+      <c r="AN87" s="359"/>
+      <c r="AO87" s="359"/>
+      <c r="AP87" s="359"/>
+      <c r="AQ87" s="359"/>
+      <c r="AR87" s="359"/>
+      <c r="AS87" s="359"/>
+      <c r="AT87" s="360"/>
       <c r="AU87" s="14"/>
     </row>
     <row r="88" spans="1:47" ht="27" customHeight="1" x14ac:dyDescent="0.35">
@@ -8859,7 +8875,7 @@
       <c r="D88" s="150"/>
       <c r="E88" s="151"/>
       <c r="F88" s="152" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G88" s="152"/>
       <c r="H88" s="152"/>
@@ -8877,7 +8893,7 @@
       <c r="T88" s="152"/>
       <c r="U88" s="152"/>
       <c r="V88" s="153" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="W88" s="153"/>
       <c r="X88" s="153"/>
@@ -8886,25 +8902,25 @@
       <c r="AA88" s="153"/>
       <c r="AB88" s="153"/>
       <c r="AC88" s="153"/>
-      <c r="AD88" s="354"/>
-      <c r="AE88" s="355"/>
-      <c r="AF88" s="356"/>
-      <c r="AG88" s="354"/>
-      <c r="AH88" s="355"/>
-      <c r="AI88" s="356"/>
-      <c r="AJ88" s="360" t="s">
-        <v>137</v>
-      </c>
-      <c r="AK88" s="361"/>
-      <c r="AL88" s="361"/>
-      <c r="AM88" s="361"/>
-      <c r="AN88" s="361"/>
-      <c r="AO88" s="361"/>
-      <c r="AP88" s="361"/>
-      <c r="AQ88" s="361"/>
-      <c r="AR88" s="361"/>
-      <c r="AS88" s="361"/>
-      <c r="AT88" s="362"/>
+      <c r="AD88" s="355"/>
+      <c r="AE88" s="356"/>
+      <c r="AF88" s="357"/>
+      <c r="AG88" s="355"/>
+      <c r="AH88" s="356"/>
+      <c r="AI88" s="357"/>
+      <c r="AJ88" s="361" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK88" s="362"/>
+      <c r="AL88" s="362"/>
+      <c r="AM88" s="362"/>
+      <c r="AN88" s="362"/>
+      <c r="AO88" s="362"/>
+      <c r="AP88" s="362"/>
+      <c r="AQ88" s="362"/>
+      <c r="AR88" s="362"/>
+      <c r="AS88" s="362"/>
+      <c r="AT88" s="363"/>
       <c r="AU88" s="14"/>
     </row>
     <row r="89" spans="1:47" ht="27" customHeight="1" x14ac:dyDescent="0.35">
@@ -8916,7 +8932,7 @@
       <c r="D89" s="150"/>
       <c r="E89" s="151"/>
       <c r="F89" s="152" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G89" s="152"/>
       <c r="H89" s="152"/>
@@ -8941,125 +8957,125 @@
       <c r="AA89" s="153"/>
       <c r="AB89" s="153"/>
       <c r="AC89" s="153"/>
-      <c r="AD89" s="354" t="s">
-        <v>135</v>
-      </c>
-      <c r="AE89" s="355"/>
-      <c r="AF89" s="356"/>
-      <c r="AG89" s="354"/>
-      <c r="AH89" s="355"/>
-      <c r="AI89" s="356"/>
-      <c r="AJ89" s="357"/>
-      <c r="AK89" s="358"/>
-      <c r="AL89" s="358"/>
-      <c r="AM89" s="358"/>
-      <c r="AN89" s="358"/>
-      <c r="AO89" s="358"/>
-      <c r="AP89" s="358"/>
-      <c r="AQ89" s="358"/>
-      <c r="AR89" s="358"/>
-      <c r="AS89" s="358"/>
-      <c r="AT89" s="359"/>
+      <c r="AD89" s="355" t="s">
+        <v>133</v>
+      </c>
+      <c r="AE89" s="356"/>
+      <c r="AF89" s="357"/>
+      <c r="AG89" s="355"/>
+      <c r="AH89" s="356"/>
+      <c r="AI89" s="357"/>
+      <c r="AJ89" s="358"/>
+      <c r="AK89" s="359"/>
+      <c r="AL89" s="359"/>
+      <c r="AM89" s="359"/>
+      <c r="AN89" s="359"/>
+      <c r="AO89" s="359"/>
+      <c r="AP89" s="359"/>
+      <c r="AQ89" s="359"/>
+      <c r="AR89" s="359"/>
+      <c r="AS89" s="359"/>
+      <c r="AT89" s="360"/>
       <c r="AU89" s="14"/>
     </row>
     <row r="90" spans="1:47" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="13"/>
-      <c r="B90" s="353" t="s">
+      <c r="B90" s="354" t="s">
         <v>79</v>
       </c>
-      <c r="C90" s="353"/>
-      <c r="D90" s="353"/>
-      <c r="E90" s="353"/>
-      <c r="F90" s="353"/>
-      <c r="G90" s="353"/>
-      <c r="H90" s="353"/>
-      <c r="I90" s="353"/>
-      <c r="J90" s="353"/>
-      <c r="K90" s="353"/>
-      <c r="L90" s="353"/>
-      <c r="M90" s="353"/>
-      <c r="N90" s="353"/>
-      <c r="O90" s="353"/>
-      <c r="P90" s="353"/>
-      <c r="Q90" s="353"/>
-      <c r="R90" s="353"/>
-      <c r="S90" s="353"/>
-      <c r="T90" s="353"/>
-      <c r="U90" s="353"/>
-      <c r="V90" s="353"/>
-      <c r="W90" s="353"/>
-      <c r="X90" s="353"/>
-      <c r="Y90" s="353"/>
-      <c r="Z90" s="353"/>
-      <c r="AA90" s="353"/>
-      <c r="AB90" s="353"/>
-      <c r="AC90" s="353"/>
-      <c r="AD90" s="353"/>
-      <c r="AE90" s="353"/>
-      <c r="AF90" s="353"/>
-      <c r="AG90" s="353"/>
-      <c r="AH90" s="353"/>
-      <c r="AI90" s="353"/>
-      <c r="AJ90" s="353"/>
-      <c r="AK90" s="353"/>
-      <c r="AL90" s="353"/>
-      <c r="AM90" s="353"/>
-      <c r="AN90" s="353"/>
-      <c r="AO90" s="353"/>
-      <c r="AP90" s="353"/>
-      <c r="AQ90" s="353"/>
-      <c r="AR90" s="353"/>
-      <c r="AS90" s="353"/>
-      <c r="AT90" s="353"/>
+      <c r="C90" s="354"/>
+      <c r="D90" s="354"/>
+      <c r="E90" s="354"/>
+      <c r="F90" s="354"/>
+      <c r="G90" s="354"/>
+      <c r="H90" s="354"/>
+      <c r="I90" s="354"/>
+      <c r="J90" s="354"/>
+      <c r="K90" s="354"/>
+      <c r="L90" s="354"/>
+      <c r="M90" s="354"/>
+      <c r="N90" s="354"/>
+      <c r="O90" s="354"/>
+      <c r="P90" s="354"/>
+      <c r="Q90" s="354"/>
+      <c r="R90" s="354"/>
+      <c r="S90" s="354"/>
+      <c r="T90" s="354"/>
+      <c r="U90" s="354"/>
+      <c r="V90" s="354"/>
+      <c r="W90" s="354"/>
+      <c r="X90" s="354"/>
+      <c r="Y90" s="354"/>
+      <c r="Z90" s="354"/>
+      <c r="AA90" s="354"/>
+      <c r="AB90" s="354"/>
+      <c r="AC90" s="354"/>
+      <c r="AD90" s="354"/>
+      <c r="AE90" s="354"/>
+      <c r="AF90" s="354"/>
+      <c r="AG90" s="354"/>
+      <c r="AH90" s="354"/>
+      <c r="AI90" s="354"/>
+      <c r="AJ90" s="354"/>
+      <c r="AK90" s="354"/>
+      <c r="AL90" s="354"/>
+      <c r="AM90" s="354"/>
+      <c r="AN90" s="354"/>
+      <c r="AO90" s="354"/>
+      <c r="AP90" s="354"/>
+      <c r="AQ90" s="354"/>
+      <c r="AR90" s="354"/>
+      <c r="AS90" s="354"/>
+      <c r="AT90" s="354"/>
       <c r="AU90" s="14"/>
     </row>
     <row r="91" spans="1:47" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A91" s="13"/>
-      <c r="B91" s="350"/>
-      <c r="C91" s="351"/>
-      <c r="D91" s="351"/>
-      <c r="E91" s="351"/>
-      <c r="F91" s="351"/>
-      <c r="G91" s="351"/>
-      <c r="H91" s="351"/>
-      <c r="I91" s="351"/>
-      <c r="J91" s="351"/>
-      <c r="K91" s="351"/>
-      <c r="L91" s="351"/>
-      <c r="M91" s="351"/>
-      <c r="N91" s="351"/>
-      <c r="O91" s="351"/>
-      <c r="P91" s="351"/>
-      <c r="Q91" s="351"/>
-      <c r="R91" s="351"/>
-      <c r="S91" s="351"/>
-      <c r="T91" s="351"/>
-      <c r="U91" s="351"/>
-      <c r="V91" s="351"/>
-      <c r="W91" s="351"/>
-      <c r="X91" s="351"/>
-      <c r="Y91" s="351"/>
-      <c r="Z91" s="351"/>
-      <c r="AA91" s="351"/>
-      <c r="AB91" s="351"/>
-      <c r="AC91" s="351"/>
-      <c r="AD91" s="351"/>
-      <c r="AE91" s="351"/>
-      <c r="AF91" s="351"/>
-      <c r="AG91" s="351"/>
-      <c r="AH91" s="351"/>
-      <c r="AI91" s="351"/>
-      <c r="AJ91" s="351"/>
-      <c r="AK91" s="351"/>
-      <c r="AL91" s="351"/>
-      <c r="AM91" s="351"/>
-      <c r="AN91" s="351"/>
-      <c r="AO91" s="351"/>
-      <c r="AP91" s="351"/>
-      <c r="AQ91" s="351"/>
-      <c r="AR91" s="351"/>
-      <c r="AS91" s="351"/>
-      <c r="AT91" s="352"/>
+      <c r="B91" s="351"/>
+      <c r="C91" s="352"/>
+      <c r="D91" s="352"/>
+      <c r="E91" s="352"/>
+      <c r="F91" s="352"/>
+      <c r="G91" s="352"/>
+      <c r="H91" s="352"/>
+      <c r="I91" s="352"/>
+      <c r="J91" s="352"/>
+      <c r="K91" s="352"/>
+      <c r="L91" s="352"/>
+      <c r="M91" s="352"/>
+      <c r="N91" s="352"/>
+      <c r="O91" s="352"/>
+      <c r="P91" s="352"/>
+      <c r="Q91" s="352"/>
+      <c r="R91" s="352"/>
+      <c r="S91" s="352"/>
+      <c r="T91" s="352"/>
+      <c r="U91" s="352"/>
+      <c r="V91" s="352"/>
+      <c r="W91" s="352"/>
+      <c r="X91" s="352"/>
+      <c r="Y91" s="352"/>
+      <c r="Z91" s="352"/>
+      <c r="AA91" s="352"/>
+      <c r="AB91" s="352"/>
+      <c r="AC91" s="352"/>
+      <c r="AD91" s="352"/>
+      <c r="AE91" s="352"/>
+      <c r="AF91" s="352"/>
+      <c r="AG91" s="352"/>
+      <c r="AH91" s="352"/>
+      <c r="AI91" s="352"/>
+      <c r="AJ91" s="352"/>
+      <c r="AK91" s="352"/>
+      <c r="AL91" s="352"/>
+      <c r="AM91" s="352"/>
+      <c r="AN91" s="352"/>
+      <c r="AO91" s="352"/>
+      <c r="AP91" s="352"/>
+      <c r="AQ91" s="352"/>
+      <c r="AR91" s="352"/>
+      <c r="AS91" s="352"/>
+      <c r="AT91" s="353"/>
       <c r="AU91" s="14"/>
     </row>
     <row r="92" spans="1:47" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -9162,53 +9178,53 @@
     </row>
     <row r="94" spans="1:47" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="13"/>
-      <c r="B94" s="394" t="s">
+      <c r="B94" s="395" t="s">
         <v>77</v>
       </c>
-      <c r="C94" s="394"/>
-      <c r="D94" s="394"/>
-      <c r="E94" s="394"/>
-      <c r="F94" s="394"/>
-      <c r="G94" s="394"/>
-      <c r="H94" s="394"/>
-      <c r="I94" s="394"/>
-      <c r="J94" s="394"/>
-      <c r="K94" s="394"/>
-      <c r="L94" s="394"/>
-      <c r="M94" s="394"/>
-      <c r="N94" s="394"/>
-      <c r="O94" s="394"/>
-      <c r="P94" s="394"/>
-      <c r="Q94" s="394"/>
-      <c r="R94" s="394"/>
-      <c r="S94" s="394"/>
-      <c r="T94" s="394"/>
-      <c r="U94" s="394"/>
-      <c r="V94" s="394"/>
-      <c r="W94" s="394"/>
-      <c r="X94" s="394"/>
-      <c r="Y94" s="394"/>
-      <c r="Z94" s="394"/>
-      <c r="AA94" s="394"/>
-      <c r="AB94" s="394"/>
-      <c r="AC94" s="394"/>
-      <c r="AD94" s="394"/>
-      <c r="AE94" s="394"/>
-      <c r="AF94" s="394"/>
-      <c r="AG94" s="394"/>
-      <c r="AH94" s="394"/>
-      <c r="AI94" s="394"/>
-      <c r="AJ94" s="394"/>
-      <c r="AK94" s="394"/>
-      <c r="AL94" s="394"/>
-      <c r="AM94" s="394"/>
-      <c r="AN94" s="394"/>
-      <c r="AO94" s="394"/>
-      <c r="AP94" s="394"/>
-      <c r="AQ94" s="394"/>
-      <c r="AR94" s="394"/>
-      <c r="AS94" s="394"/>
-      <c r="AT94" s="394"/>
+      <c r="C94" s="395"/>
+      <c r="D94" s="395"/>
+      <c r="E94" s="395"/>
+      <c r="F94" s="395"/>
+      <c r="G94" s="395"/>
+      <c r="H94" s="395"/>
+      <c r="I94" s="395"/>
+      <c r="J94" s="395"/>
+      <c r="K94" s="395"/>
+      <c r="L94" s="395"/>
+      <c r="M94" s="395"/>
+      <c r="N94" s="395"/>
+      <c r="O94" s="395"/>
+      <c r="P94" s="395"/>
+      <c r="Q94" s="395"/>
+      <c r="R94" s="395"/>
+      <c r="S94" s="395"/>
+      <c r="T94" s="395"/>
+      <c r="U94" s="395"/>
+      <c r="V94" s="395"/>
+      <c r="W94" s="395"/>
+      <c r="X94" s="395"/>
+      <c r="Y94" s="395"/>
+      <c r="Z94" s="395"/>
+      <c r="AA94" s="395"/>
+      <c r="AB94" s="395"/>
+      <c r="AC94" s="395"/>
+      <c r="AD94" s="395"/>
+      <c r="AE94" s="395"/>
+      <c r="AF94" s="395"/>
+      <c r="AG94" s="395"/>
+      <c r="AH94" s="395"/>
+      <c r="AI94" s="395"/>
+      <c r="AJ94" s="395"/>
+      <c r="AK94" s="395"/>
+      <c r="AL94" s="395"/>
+      <c r="AM94" s="395"/>
+      <c r="AN94" s="395"/>
+      <c r="AO94" s="395"/>
+      <c r="AP94" s="395"/>
+      <c r="AQ94" s="395"/>
+      <c r="AR94" s="395"/>
+      <c r="AS94" s="395"/>
+      <c r="AT94" s="395"/>
       <c r="AU94" s="14"/>
     </row>
     <row r="95" spans="1:47" ht="12.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -9262,149 +9278,149 @@
     </row>
     <row r="96" spans="1:47" ht="12.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="13"/>
-      <c r="B96" s="335"/>
-      <c r="C96" s="336"/>
-      <c r="D96" s="336"/>
-      <c r="E96" s="336"/>
-      <c r="F96" s="336"/>
-      <c r="G96" s="336"/>
-      <c r="H96" s="336"/>
-      <c r="I96" s="336"/>
-      <c r="J96" s="336"/>
-      <c r="K96" s="336"/>
-      <c r="L96" s="336"/>
-      <c r="M96" s="336"/>
-      <c r="N96" s="336"/>
-      <c r="O96" s="336"/>
-      <c r="P96" s="336"/>
-      <c r="Q96" s="336"/>
-      <c r="R96" s="336"/>
-      <c r="S96" s="336"/>
-      <c r="T96" s="336"/>
-      <c r="U96" s="336"/>
-      <c r="V96" s="336"/>
-      <c r="W96" s="336"/>
-      <c r="X96" s="336"/>
-      <c r="Y96" s="336"/>
-      <c r="Z96" s="336"/>
-      <c r="AA96" s="336"/>
-      <c r="AB96" s="336"/>
-      <c r="AC96" s="336"/>
-      <c r="AD96" s="336"/>
-      <c r="AE96" s="336"/>
-      <c r="AF96" s="336"/>
-      <c r="AG96" s="336"/>
-      <c r="AH96" s="336"/>
-      <c r="AI96" s="336"/>
-      <c r="AJ96" s="336"/>
-      <c r="AK96" s="336"/>
-      <c r="AL96" s="336"/>
-      <c r="AM96" s="336"/>
-      <c r="AN96" s="336"/>
-      <c r="AO96" s="336"/>
-      <c r="AP96" s="336"/>
-      <c r="AQ96" s="336"/>
-      <c r="AR96" s="336"/>
-      <c r="AS96" s="336"/>
-      <c r="AT96" s="337"/>
+      <c r="B96" s="336"/>
+      <c r="C96" s="337"/>
+      <c r="D96" s="337"/>
+      <c r="E96" s="337"/>
+      <c r="F96" s="337"/>
+      <c r="G96" s="337"/>
+      <c r="H96" s="337"/>
+      <c r="I96" s="337"/>
+      <c r="J96" s="337"/>
+      <c r="K96" s="337"/>
+      <c r="L96" s="337"/>
+      <c r="M96" s="337"/>
+      <c r="N96" s="337"/>
+      <c r="O96" s="337"/>
+      <c r="P96" s="337"/>
+      <c r="Q96" s="337"/>
+      <c r="R96" s="337"/>
+      <c r="S96" s="337"/>
+      <c r="T96" s="337"/>
+      <c r="U96" s="337"/>
+      <c r="V96" s="337"/>
+      <c r="W96" s="337"/>
+      <c r="X96" s="337"/>
+      <c r="Y96" s="337"/>
+      <c r="Z96" s="337"/>
+      <c r="AA96" s="337"/>
+      <c r="AB96" s="337"/>
+      <c r="AC96" s="337"/>
+      <c r="AD96" s="337"/>
+      <c r="AE96" s="337"/>
+      <c r="AF96" s="337"/>
+      <c r="AG96" s="337"/>
+      <c r="AH96" s="337"/>
+      <c r="AI96" s="337"/>
+      <c r="AJ96" s="337"/>
+      <c r="AK96" s="337"/>
+      <c r="AL96" s="337"/>
+      <c r="AM96" s="337"/>
+      <c r="AN96" s="337"/>
+      <c r="AO96" s="337"/>
+      <c r="AP96" s="337"/>
+      <c r="AQ96" s="337"/>
+      <c r="AR96" s="337"/>
+      <c r="AS96" s="337"/>
+      <c r="AT96" s="338"/>
       <c r="AU96" s="14"/>
     </row>
     <row r="97" spans="1:47" ht="12.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="13"/>
-      <c r="B97" s="338"/>
-      <c r="C97" s="339"/>
-      <c r="D97" s="339"/>
-      <c r="E97" s="339"/>
-      <c r="F97" s="339"/>
-      <c r="G97" s="339"/>
-      <c r="H97" s="339"/>
-      <c r="I97" s="339"/>
-      <c r="J97" s="339"/>
-      <c r="K97" s="339"/>
-      <c r="L97" s="339"/>
-      <c r="M97" s="339"/>
-      <c r="N97" s="339"/>
-      <c r="O97" s="339"/>
-      <c r="P97" s="339"/>
-      <c r="Q97" s="339"/>
-      <c r="R97" s="339"/>
-      <c r="S97" s="339"/>
-      <c r="T97" s="339"/>
-      <c r="U97" s="339"/>
-      <c r="V97" s="339"/>
-      <c r="W97" s="339"/>
-      <c r="X97" s="339"/>
-      <c r="Y97" s="339"/>
-      <c r="Z97" s="339"/>
-      <c r="AA97" s="339"/>
-      <c r="AB97" s="339"/>
-      <c r="AC97" s="339"/>
-      <c r="AD97" s="339"/>
-      <c r="AE97" s="339"/>
-      <c r="AF97" s="339"/>
-      <c r="AG97" s="339"/>
-      <c r="AH97" s="339"/>
-      <c r="AI97" s="339"/>
-      <c r="AJ97" s="339"/>
-      <c r="AK97" s="339"/>
-      <c r="AL97" s="339"/>
-      <c r="AM97" s="339"/>
-      <c r="AN97" s="339"/>
-      <c r="AO97" s="339"/>
-      <c r="AP97" s="339"/>
-      <c r="AQ97" s="339"/>
-      <c r="AR97" s="339"/>
-      <c r="AS97" s="339"/>
-      <c r="AT97" s="340"/>
+      <c r="B97" s="339"/>
+      <c r="C97" s="340"/>
+      <c r="D97" s="340"/>
+      <c r="E97" s="340"/>
+      <c r="F97" s="340"/>
+      <c r="G97" s="340"/>
+      <c r="H97" s="340"/>
+      <c r="I97" s="340"/>
+      <c r="J97" s="340"/>
+      <c r="K97" s="340"/>
+      <c r="L97" s="340"/>
+      <c r="M97" s="340"/>
+      <c r="N97" s="340"/>
+      <c r="O97" s="340"/>
+      <c r="P97" s="340"/>
+      <c r="Q97" s="340"/>
+      <c r="R97" s="340"/>
+      <c r="S97" s="340"/>
+      <c r="T97" s="340"/>
+      <c r="U97" s="340"/>
+      <c r="V97" s="340"/>
+      <c r="W97" s="340"/>
+      <c r="X97" s="340"/>
+      <c r="Y97" s="340"/>
+      <c r="Z97" s="340"/>
+      <c r="AA97" s="340"/>
+      <c r="AB97" s="340"/>
+      <c r="AC97" s="340"/>
+      <c r="AD97" s="340"/>
+      <c r="AE97" s="340"/>
+      <c r="AF97" s="340"/>
+      <c r="AG97" s="340"/>
+      <c r="AH97" s="340"/>
+      <c r="AI97" s="340"/>
+      <c r="AJ97" s="340"/>
+      <c r="AK97" s="340"/>
+      <c r="AL97" s="340"/>
+      <c r="AM97" s="340"/>
+      <c r="AN97" s="340"/>
+      <c r="AO97" s="340"/>
+      <c r="AP97" s="340"/>
+      <c r="AQ97" s="340"/>
+      <c r="AR97" s="340"/>
+      <c r="AS97" s="340"/>
+      <c r="AT97" s="341"/>
       <c r="AU97" s="14"/>
     </row>
     <row r="98" spans="1:47" ht="12.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A98" s="13"/>
-      <c r="B98" s="341"/>
-      <c r="C98" s="342"/>
-      <c r="D98" s="342"/>
-      <c r="E98" s="342"/>
-      <c r="F98" s="342"/>
-      <c r="G98" s="342"/>
-      <c r="H98" s="342"/>
-      <c r="I98" s="342"/>
-      <c r="J98" s="342"/>
-      <c r="K98" s="342"/>
-      <c r="L98" s="342"/>
-      <c r="M98" s="342"/>
-      <c r="N98" s="342"/>
-      <c r="O98" s="342"/>
-      <c r="P98" s="342"/>
-      <c r="Q98" s="342"/>
-      <c r="R98" s="342"/>
-      <c r="S98" s="342"/>
-      <c r="T98" s="342"/>
-      <c r="U98" s="342"/>
-      <c r="V98" s="342"/>
-      <c r="W98" s="342"/>
-      <c r="X98" s="342"/>
-      <c r="Y98" s="342"/>
-      <c r="Z98" s="342"/>
-      <c r="AA98" s="342"/>
-      <c r="AB98" s="342"/>
-      <c r="AC98" s="342"/>
-      <c r="AD98" s="342"/>
-      <c r="AE98" s="342"/>
-      <c r="AF98" s="342"/>
-      <c r="AG98" s="342"/>
-      <c r="AH98" s="342"/>
-      <c r="AI98" s="342"/>
-      <c r="AJ98" s="342"/>
-      <c r="AK98" s="342"/>
-      <c r="AL98" s="342"/>
-      <c r="AM98" s="342"/>
-      <c r="AN98" s="342"/>
-      <c r="AO98" s="342"/>
-      <c r="AP98" s="342"/>
-      <c r="AQ98" s="342"/>
-      <c r="AR98" s="342"/>
-      <c r="AS98" s="342"/>
-      <c r="AT98" s="343"/>
+      <c r="B98" s="342"/>
+      <c r="C98" s="343"/>
+      <c r="D98" s="343"/>
+      <c r="E98" s="343"/>
+      <c r="F98" s="343"/>
+      <c r="G98" s="343"/>
+      <c r="H98" s="343"/>
+      <c r="I98" s="343"/>
+      <c r="J98" s="343"/>
+      <c r="K98" s="343"/>
+      <c r="L98" s="343"/>
+      <c r="M98" s="343"/>
+      <c r="N98" s="343"/>
+      <c r="O98" s="343"/>
+      <c r="P98" s="343"/>
+      <c r="Q98" s="343"/>
+      <c r="R98" s="343"/>
+      <c r="S98" s="343"/>
+      <c r="T98" s="343"/>
+      <c r="U98" s="343"/>
+      <c r="V98" s="343"/>
+      <c r="W98" s="343"/>
+      <c r="X98" s="343"/>
+      <c r="Y98" s="343"/>
+      <c r="Z98" s="343"/>
+      <c r="AA98" s="343"/>
+      <c r="AB98" s="343"/>
+      <c r="AC98" s="343"/>
+      <c r="AD98" s="343"/>
+      <c r="AE98" s="343"/>
+      <c r="AF98" s="343"/>
+      <c r="AG98" s="343"/>
+      <c r="AH98" s="343"/>
+      <c r="AI98" s="343"/>
+      <c r="AJ98" s="343"/>
+      <c r="AK98" s="343"/>
+      <c r="AL98" s="343"/>
+      <c r="AM98" s="343"/>
+      <c r="AN98" s="343"/>
+      <c r="AO98" s="343"/>
+      <c r="AP98" s="343"/>
+      <c r="AQ98" s="343"/>
+      <c r="AR98" s="343"/>
+      <c r="AS98" s="343"/>
+      <c r="AT98" s="344"/>
       <c r="AU98" s="14"/>
     </row>
     <row r="99" spans="1:47" ht="12.65" customHeight="1" x14ac:dyDescent="0.35">
@@ -9558,51 +9574,51 @@
     </row>
     <row r="102" spans="1:47" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="13"/>
-      <c r="B102" s="350"/>
-      <c r="C102" s="351"/>
-      <c r="D102" s="351"/>
-      <c r="E102" s="351"/>
-      <c r="F102" s="351"/>
-      <c r="G102" s="351"/>
-      <c r="H102" s="351"/>
-      <c r="I102" s="351"/>
-      <c r="J102" s="351"/>
-      <c r="K102" s="351"/>
-      <c r="L102" s="351"/>
-      <c r="M102" s="351"/>
-      <c r="N102" s="351"/>
-      <c r="O102" s="351"/>
-      <c r="P102" s="351"/>
-      <c r="Q102" s="351"/>
-      <c r="R102" s="351"/>
-      <c r="S102" s="351"/>
-      <c r="T102" s="351"/>
-      <c r="U102" s="351"/>
-      <c r="V102" s="351"/>
-      <c r="W102" s="351"/>
-      <c r="X102" s="351"/>
-      <c r="Y102" s="351"/>
-      <c r="Z102" s="351"/>
-      <c r="AA102" s="351"/>
-      <c r="AB102" s="351"/>
-      <c r="AC102" s="351"/>
-      <c r="AD102" s="351"/>
-      <c r="AE102" s="351"/>
-      <c r="AF102" s="351"/>
-      <c r="AG102" s="351"/>
-      <c r="AH102" s="351"/>
-      <c r="AI102" s="351"/>
-      <c r="AJ102" s="351"/>
-      <c r="AK102" s="351"/>
-      <c r="AL102" s="351"/>
-      <c r="AM102" s="351"/>
-      <c r="AN102" s="351"/>
-      <c r="AO102" s="351"/>
-      <c r="AP102" s="351"/>
-      <c r="AQ102" s="351"/>
-      <c r="AR102" s="351"/>
-      <c r="AS102" s="351"/>
-      <c r="AT102" s="352"/>
+      <c r="B102" s="351"/>
+      <c r="C102" s="352"/>
+      <c r="D102" s="352"/>
+      <c r="E102" s="352"/>
+      <c r="F102" s="352"/>
+      <c r="G102" s="352"/>
+      <c r="H102" s="352"/>
+      <c r="I102" s="352"/>
+      <c r="J102" s="352"/>
+      <c r="K102" s="352"/>
+      <c r="L102" s="352"/>
+      <c r="M102" s="352"/>
+      <c r="N102" s="352"/>
+      <c r="O102" s="352"/>
+      <c r="P102" s="352"/>
+      <c r="Q102" s="352"/>
+      <c r="R102" s="352"/>
+      <c r="S102" s="352"/>
+      <c r="T102" s="352"/>
+      <c r="U102" s="352"/>
+      <c r="V102" s="352"/>
+      <c r="W102" s="352"/>
+      <c r="X102" s="352"/>
+      <c r="Y102" s="352"/>
+      <c r="Z102" s="352"/>
+      <c r="AA102" s="352"/>
+      <c r="AB102" s="352"/>
+      <c r="AC102" s="352"/>
+      <c r="AD102" s="352"/>
+      <c r="AE102" s="352"/>
+      <c r="AF102" s="352"/>
+      <c r="AG102" s="352"/>
+      <c r="AH102" s="352"/>
+      <c r="AI102" s="352"/>
+      <c r="AJ102" s="352"/>
+      <c r="AK102" s="352"/>
+      <c r="AL102" s="352"/>
+      <c r="AM102" s="352"/>
+      <c r="AN102" s="352"/>
+      <c r="AO102" s="352"/>
+      <c r="AP102" s="352"/>
+      <c r="AQ102" s="352"/>
+      <c r="AR102" s="352"/>
+      <c r="AS102" s="352"/>
+      <c r="AT102" s="353"/>
       <c r="AU102" s="14"/>
     </row>
     <row r="103" spans="1:47" ht="12.65" customHeight="1" x14ac:dyDescent="0.35">
@@ -9869,7 +9885,7 @@
       <c r="AQ107" s="104"/>
       <c r="AR107" s="104"/>
       <c r="AS107" s="104"/>
-      <c r="AT107" s="395"/>
+      <c r="AT107" s="396"/>
       <c r="AU107" s="14"/>
     </row>
     <row r="108" spans="1:47" ht="51" customHeight="1" x14ac:dyDescent="0.35">
@@ -9877,15 +9893,15 @@
       <c r="B108" s="54">
         <v>1</v>
       </c>
-      <c r="C108" s="374">
+      <c r="C108" s="375">
         <v>45975</v>
       </c>
-      <c r="D108" s="374"/>
-      <c r="E108" s="374"/>
-      <c r="F108" s="374"/>
-      <c r="G108" s="374"/>
+      <c r="D108" s="375"/>
+      <c r="E108" s="375"/>
+      <c r="F108" s="375"/>
+      <c r="G108" s="375"/>
       <c r="H108" s="107" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I108" s="107"/>
       <c r="J108" s="107"/>
@@ -9910,33 +9926,33 @@
         <v>9646</v>
       </c>
       <c r="W108" s="107"/>
-      <c r="X108" s="376" t="s">
-        <v>134</v>
-      </c>
-      <c r="Y108" s="376"/>
-      <c r="Z108" s="376"/>
-      <c r="AA108" s="376"/>
-      <c r="AB108" s="376"/>
-      <c r="AC108" s="376"/>
-      <c r="AD108" s="376"/>
-      <c r="AE108" s="376"/>
-      <c r="AF108" s="376"/>
-      <c r="AG108" s="376"/>
-      <c r="AH108" s="376"/>
-      <c r="AI108" s="376"/>
-      <c r="AJ108" s="376"/>
-      <c r="AK108" s="376"/>
-      <c r="AL108" s="376"/>
-      <c r="AM108" s="376"/>
-      <c r="AN108" s="366">
+      <c r="X108" s="377" t="s">
+        <v>132</v>
+      </c>
+      <c r="Y108" s="377"/>
+      <c r="Z108" s="377"/>
+      <c r="AA108" s="377"/>
+      <c r="AB108" s="377"/>
+      <c r="AC108" s="377"/>
+      <c r="AD108" s="377"/>
+      <c r="AE108" s="377"/>
+      <c r="AF108" s="377"/>
+      <c r="AG108" s="377"/>
+      <c r="AH108" s="377"/>
+      <c r="AI108" s="377"/>
+      <c r="AJ108" s="377"/>
+      <c r="AK108" s="377"/>
+      <c r="AL108" s="377"/>
+      <c r="AM108" s="377"/>
+      <c r="AN108" s="367">
         <v>27331418.760000002</v>
       </c>
-      <c r="AO108" s="366"/>
-      <c r="AP108" s="366"/>
-      <c r="AQ108" s="366"/>
-      <c r="AR108" s="366"/>
-      <c r="AS108" s="366"/>
-      <c r="AT108" s="367"/>
+      <c r="AO108" s="367"/>
+      <c r="AP108" s="367"/>
+      <c r="AQ108" s="367"/>
+      <c r="AR108" s="367"/>
+      <c r="AS108" s="367"/>
+      <c r="AT108" s="368"/>
       <c r="AU108" s="14"/>
     </row>
     <row r="109" spans="1:47" ht="13" x14ac:dyDescent="0.35">
@@ -10097,43 +10113,43 @@
       <c r="B112" s="40">
         <v>5</v>
       </c>
-      <c r="C112" s="371"/>
-      <c r="D112" s="371"/>
-      <c r="E112" s="371"/>
-      <c r="F112" s="371"/>
-      <c r="G112" s="371"/>
-      <c r="H112" s="371"/>
-      <c r="I112" s="371"/>
-      <c r="J112" s="371"/>
-      <c r="K112" s="371"/>
-      <c r="L112" s="371"/>
-      <c r="M112" s="372"/>
-      <c r="N112" s="372"/>
-      <c r="O112" s="372"/>
-      <c r="P112" s="372"/>
-      <c r="Q112" s="372"/>
-      <c r="R112" s="372"/>
-      <c r="S112" s="372"/>
-      <c r="T112" s="372"/>
-      <c r="U112" s="372"/>
-      <c r="V112" s="372"/>
-      <c r="W112" s="372"/>
-      <c r="X112" s="371"/>
-      <c r="Y112" s="371"/>
-      <c r="Z112" s="371"/>
-      <c r="AA112" s="371"/>
-      <c r="AB112" s="371"/>
-      <c r="AC112" s="371"/>
-      <c r="AD112" s="371"/>
-      <c r="AE112" s="371"/>
-      <c r="AF112" s="371"/>
-      <c r="AG112" s="371"/>
-      <c r="AH112" s="371"/>
-      <c r="AI112" s="371"/>
-      <c r="AJ112" s="371"/>
-      <c r="AK112" s="371"/>
-      <c r="AL112" s="371"/>
-      <c r="AM112" s="371"/>
+      <c r="C112" s="372"/>
+      <c r="D112" s="372"/>
+      <c r="E112" s="372"/>
+      <c r="F112" s="372"/>
+      <c r="G112" s="372"/>
+      <c r="H112" s="372"/>
+      <c r="I112" s="372"/>
+      <c r="J112" s="372"/>
+      <c r="K112" s="372"/>
+      <c r="L112" s="372"/>
+      <c r="M112" s="373"/>
+      <c r="N112" s="373"/>
+      <c r="O112" s="373"/>
+      <c r="P112" s="373"/>
+      <c r="Q112" s="373"/>
+      <c r="R112" s="373"/>
+      <c r="S112" s="373"/>
+      <c r="T112" s="373"/>
+      <c r="U112" s="373"/>
+      <c r="V112" s="373"/>
+      <c r="W112" s="373"/>
+      <c r="X112" s="372"/>
+      <c r="Y112" s="372"/>
+      <c r="Z112" s="372"/>
+      <c r="AA112" s="372"/>
+      <c r="AB112" s="372"/>
+      <c r="AC112" s="372"/>
+      <c r="AD112" s="372"/>
+      <c r="AE112" s="372"/>
+      <c r="AF112" s="372"/>
+      <c r="AG112" s="372"/>
+      <c r="AH112" s="372"/>
+      <c r="AI112" s="372"/>
+      <c r="AJ112" s="372"/>
+      <c r="AK112" s="372"/>
+      <c r="AL112" s="372"/>
+      <c r="AM112" s="372"/>
       <c r="AN112" s="200"/>
       <c r="AO112" s="200"/>
       <c r="AP112" s="200"/>
@@ -10185,16 +10201,16 @@
       <c r="AM113" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="AN113" s="368">
+      <c r="AN113" s="369">
         <f>SUM(AN108:AT112)</f>
         <v>27331418.760000002</v>
       </c>
-      <c r="AO113" s="369"/>
-      <c r="AP113" s="369"/>
-      <c r="AQ113" s="369"/>
-      <c r="AR113" s="369"/>
-      <c r="AS113" s="369"/>
-      <c r="AT113" s="370"/>
+      <c r="AO113" s="370"/>
+      <c r="AP113" s="370"/>
+      <c r="AQ113" s="370"/>
+      <c r="AR113" s="370"/>
+      <c r="AS113" s="370"/>
+      <c r="AT113" s="371"/>
       <c r="AU113" s="14"/>
     </row>
     <row r="114" spans="1:52" ht="12.65" customHeight="1" x14ac:dyDescent="0.35">
@@ -10231,19 +10247,19 @@
       <c r="AE114" s="2"/>
       <c r="AF114" s="2"/>
       <c r="AG114" s="2"/>
-      <c r="AH114" s="373"/>
-      <c r="AI114" s="373"/>
-      <c r="AJ114" s="373"/>
-      <c r="AK114" s="373"/>
-      <c r="AL114" s="373"/>
-      <c r="AM114" s="373"/>
-      <c r="AN114" s="373"/>
-      <c r="AO114" s="373"/>
-      <c r="AP114" s="373"/>
-      <c r="AQ114" s="373"/>
-      <c r="AR114" s="373"/>
-      <c r="AS114" s="373"/>
-      <c r="AT114" s="373"/>
+      <c r="AH114" s="374"/>
+      <c r="AI114" s="374"/>
+      <c r="AJ114" s="374"/>
+      <c r="AK114" s="374"/>
+      <c r="AL114" s="374"/>
+      <c r="AM114" s="374"/>
+      <c r="AN114" s="374"/>
+      <c r="AO114" s="374"/>
+      <c r="AP114" s="374"/>
+      <c r="AQ114" s="374"/>
+      <c r="AR114" s="374"/>
+      <c r="AS114" s="374"/>
+      <c r="AT114" s="374"/>
       <c r="AU114" s="14"/>
     </row>
     <row r="115" spans="1:52" ht="12.65" customHeight="1" x14ac:dyDescent="0.35">
@@ -10280,19 +10296,19 @@
       <c r="AE115" s="2"/>
       <c r="AF115" s="2"/>
       <c r="AG115" s="2"/>
-      <c r="AH115" s="373"/>
-      <c r="AI115" s="373"/>
-      <c r="AJ115" s="373"/>
-      <c r="AK115" s="373"/>
-      <c r="AL115" s="373"/>
-      <c r="AM115" s="373"/>
-      <c r="AN115" s="373"/>
-      <c r="AO115" s="373"/>
-      <c r="AP115" s="373"/>
-      <c r="AQ115" s="373"/>
-      <c r="AR115" s="373"/>
-      <c r="AS115" s="373"/>
-      <c r="AT115" s="373"/>
+      <c r="AH115" s="374"/>
+      <c r="AI115" s="374"/>
+      <c r="AJ115" s="374"/>
+      <c r="AK115" s="374"/>
+      <c r="AL115" s="374"/>
+      <c r="AM115" s="374"/>
+      <c r="AN115" s="374"/>
+      <c r="AO115" s="374"/>
+      <c r="AP115" s="374"/>
+      <c r="AQ115" s="374"/>
+      <c r="AR115" s="374"/>
+      <c r="AS115" s="374"/>
+      <c r="AT115" s="374"/>
       <c r="AU115" s="14"/>
     </row>
     <row r="116" spans="1:52" ht="12.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -10365,25 +10381,25 @@
       <c r="J117" s="206"/>
       <c r="K117" s="206"/>
       <c r="L117" s="206"/>
-      <c r="M117" s="381" t="s">
+      <c r="M117" s="382" t="s">
         <v>48</v>
       </c>
-      <c r="N117" s="381"/>
-      <c r="O117" s="381"/>
-      <c r="P117" s="381" t="s">
+      <c r="N117" s="382"/>
+      <c r="O117" s="382"/>
+      <c r="P117" s="382" t="s">
         <v>59</v>
       </c>
-      <c r="Q117" s="381"/>
-      <c r="R117" s="381"/>
-      <c r="S117" s="381" t="s">
+      <c r="Q117" s="382"/>
+      <c r="R117" s="382"/>
+      <c r="S117" s="382" t="s">
         <v>50</v>
       </c>
-      <c r="T117" s="381"/>
-      <c r="U117" s="381"/>
-      <c r="V117" s="381" t="s">
+      <c r="T117" s="382"/>
+      <c r="U117" s="382"/>
+      <c r="V117" s="382" t="s">
         <v>60</v>
       </c>
-      <c r="W117" s="381"/>
+      <c r="W117" s="382"/>
       <c r="X117" s="206" t="s">
         <v>51</v>
       </c>
@@ -10410,7 +10426,7 @@
       <c r="AQ117" s="206"/>
       <c r="AR117" s="206"/>
       <c r="AS117" s="206"/>
-      <c r="AT117" s="321"/>
+      <c r="AT117" s="322"/>
       <c r="AU117" s="62"/>
       <c r="AZ117" s="94">
         <f>+AN50</f>
@@ -10430,7 +10446,7 @@
       <c r="F118" s="178"/>
       <c r="G118" s="178"/>
       <c r="H118" s="175" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I118" s="175"/>
       <c r="J118" s="175"/>
@@ -10455,33 +10471,33 @@
         <v>9646</v>
       </c>
       <c r="W118" s="175"/>
-      <c r="X118" s="378" t="s">
-        <v>142</v>
-      </c>
-      <c r="Y118" s="378"/>
-      <c r="Z118" s="378"/>
-      <c r="AA118" s="378"/>
-      <c r="AB118" s="378"/>
-      <c r="AC118" s="378"/>
-      <c r="AD118" s="378"/>
-      <c r="AE118" s="378"/>
-      <c r="AF118" s="378"/>
-      <c r="AG118" s="378"/>
-      <c r="AH118" s="378"/>
-      <c r="AI118" s="378"/>
-      <c r="AJ118" s="378"/>
-      <c r="AK118" s="378"/>
-      <c r="AL118" s="378"/>
-      <c r="AM118" s="378"/>
-      <c r="AN118" s="392">
-        <v>22200000</v>
-      </c>
-      <c r="AO118" s="392"/>
-      <c r="AP118" s="392"/>
-      <c r="AQ118" s="392"/>
-      <c r="AR118" s="392"/>
-      <c r="AS118" s="392"/>
-      <c r="AT118" s="393"/>
+      <c r="X118" s="379" t="s">
+        <v>140</v>
+      </c>
+      <c r="Y118" s="379"/>
+      <c r="Z118" s="379"/>
+      <c r="AA118" s="379"/>
+      <c r="AB118" s="379"/>
+      <c r="AC118" s="379"/>
+      <c r="AD118" s="379"/>
+      <c r="AE118" s="379"/>
+      <c r="AF118" s="379"/>
+      <c r="AG118" s="379"/>
+      <c r="AH118" s="379"/>
+      <c r="AI118" s="379"/>
+      <c r="AJ118" s="379"/>
+      <c r="AK118" s="379"/>
+      <c r="AL118" s="379"/>
+      <c r="AM118" s="379"/>
+      <c r="AN118" s="393">
+        <v>42000000</v>
+      </c>
+      <c r="AO118" s="393"/>
+      <c r="AP118" s="393"/>
+      <c r="AQ118" s="393"/>
+      <c r="AR118" s="393"/>
+      <c r="AS118" s="393"/>
+      <c r="AT118" s="394"/>
       <c r="AU118" s="62"/>
       <c r="AZ118" s="94">
         <v>59200000</v>
@@ -10542,53 +10558,53 @@
     </row>
     <row r="120" spans="1:52" s="63" customFormat="1" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="59"/>
-      <c r="B120" s="388" t="s">
+      <c r="B120" s="389" t="s">
         <v>94</v>
       </c>
-      <c r="C120" s="388"/>
-      <c r="D120" s="388"/>
-      <c r="E120" s="388"/>
-      <c r="F120" s="388"/>
-      <c r="G120" s="388"/>
-      <c r="H120" s="388"/>
-      <c r="I120" s="388"/>
-      <c r="J120" s="388"/>
-      <c r="K120" s="388"/>
-      <c r="L120" s="388"/>
-      <c r="M120" s="388"/>
-      <c r="N120" s="388"/>
-      <c r="O120" s="388"/>
-      <c r="P120" s="388"/>
-      <c r="Q120" s="388"/>
-      <c r="R120" s="388"/>
-      <c r="S120" s="388"/>
-      <c r="T120" s="388"/>
-      <c r="U120" s="388"/>
-      <c r="V120" s="388"/>
-      <c r="W120" s="388"/>
-      <c r="X120" s="388"/>
-      <c r="Y120" s="388"/>
-      <c r="Z120" s="388"/>
-      <c r="AA120" s="388"/>
-      <c r="AB120" s="388"/>
-      <c r="AC120" s="388"/>
-      <c r="AD120" s="388"/>
-      <c r="AE120" s="388"/>
-      <c r="AF120" s="388"/>
-      <c r="AG120" s="388"/>
-      <c r="AH120" s="388"/>
-      <c r="AI120" s="388"/>
-      <c r="AJ120" s="388"/>
-      <c r="AK120" s="388"/>
-      <c r="AL120" s="388"/>
-      <c r="AM120" s="388"/>
-      <c r="AN120" s="388"/>
-      <c r="AO120" s="388"/>
-      <c r="AP120" s="388"/>
-      <c r="AQ120" s="388"/>
-      <c r="AR120" s="388"/>
-      <c r="AS120" s="388"/>
-      <c r="AT120" s="388"/>
+      <c r="C120" s="389"/>
+      <c r="D120" s="389"/>
+      <c r="E120" s="389"/>
+      <c r="F120" s="389"/>
+      <c r="G120" s="389"/>
+      <c r="H120" s="389"/>
+      <c r="I120" s="389"/>
+      <c r="J120" s="389"/>
+      <c r="K120" s="389"/>
+      <c r="L120" s="389"/>
+      <c r="M120" s="389"/>
+      <c r="N120" s="389"/>
+      <c r="O120" s="389"/>
+      <c r="P120" s="389"/>
+      <c r="Q120" s="389"/>
+      <c r="R120" s="389"/>
+      <c r="S120" s="389"/>
+      <c r="T120" s="389"/>
+      <c r="U120" s="389"/>
+      <c r="V120" s="389"/>
+      <c r="W120" s="389"/>
+      <c r="X120" s="389"/>
+      <c r="Y120" s="389"/>
+      <c r="Z120" s="389"/>
+      <c r="AA120" s="389"/>
+      <c r="AB120" s="389"/>
+      <c r="AC120" s="389"/>
+      <c r="AD120" s="389"/>
+      <c r="AE120" s="389"/>
+      <c r="AF120" s="389"/>
+      <c r="AG120" s="389"/>
+      <c r="AH120" s="389"/>
+      <c r="AI120" s="389"/>
+      <c r="AJ120" s="389"/>
+      <c r="AK120" s="389"/>
+      <c r="AL120" s="389"/>
+      <c r="AM120" s="389"/>
+      <c r="AN120" s="389"/>
+      <c r="AO120" s="389"/>
+      <c r="AP120" s="389"/>
+      <c r="AQ120" s="389"/>
+      <c r="AR120" s="389"/>
+      <c r="AS120" s="389"/>
+      <c r="AT120" s="389"/>
       <c r="AU120" s="62"/>
       <c r="AZ120" s="94"/>
     </row>
@@ -10644,53 +10660,53 @@
     </row>
     <row r="122" spans="1:52" s="63" customFormat="1" ht="28.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A122" s="59"/>
-      <c r="B122" s="389" t="s">
+      <c r="B122" s="390" t="s">
         <v>93</v>
       </c>
-      <c r="C122" s="390"/>
-      <c r="D122" s="390"/>
-      <c r="E122" s="390"/>
-      <c r="F122" s="390"/>
-      <c r="G122" s="390"/>
-      <c r="H122" s="390"/>
-      <c r="I122" s="390"/>
-      <c r="J122" s="390"/>
-      <c r="K122" s="390"/>
-      <c r="L122" s="390"/>
-      <c r="M122" s="390"/>
-      <c r="N122" s="390"/>
-      <c r="O122" s="390"/>
-      <c r="P122" s="390"/>
-      <c r="Q122" s="390"/>
-      <c r="R122" s="390"/>
-      <c r="S122" s="390"/>
-      <c r="T122" s="390"/>
-      <c r="U122" s="390"/>
-      <c r="V122" s="390"/>
-      <c r="W122" s="390"/>
-      <c r="X122" s="390"/>
-      <c r="Y122" s="390"/>
-      <c r="Z122" s="390"/>
-      <c r="AA122" s="390"/>
-      <c r="AB122" s="390"/>
-      <c r="AC122" s="390"/>
-      <c r="AD122" s="390"/>
-      <c r="AE122" s="390"/>
-      <c r="AF122" s="390"/>
-      <c r="AG122" s="390"/>
-      <c r="AH122" s="390"/>
-      <c r="AI122" s="390"/>
-      <c r="AJ122" s="390"/>
-      <c r="AK122" s="390"/>
-      <c r="AL122" s="390"/>
-      <c r="AM122" s="390"/>
-      <c r="AN122" s="390"/>
-      <c r="AO122" s="390"/>
-      <c r="AP122" s="390"/>
-      <c r="AQ122" s="390"/>
-      <c r="AR122" s="390"/>
-      <c r="AS122" s="390"/>
-      <c r="AT122" s="391"/>
+      <c r="C122" s="391"/>
+      <c r="D122" s="391"/>
+      <c r="E122" s="391"/>
+      <c r="F122" s="391"/>
+      <c r="G122" s="391"/>
+      <c r="H122" s="391"/>
+      <c r="I122" s="391"/>
+      <c r="J122" s="391"/>
+      <c r="K122" s="391"/>
+      <c r="L122" s="391"/>
+      <c r="M122" s="391"/>
+      <c r="N122" s="391"/>
+      <c r="O122" s="391"/>
+      <c r="P122" s="391"/>
+      <c r="Q122" s="391"/>
+      <c r="R122" s="391"/>
+      <c r="S122" s="391"/>
+      <c r="T122" s="391"/>
+      <c r="U122" s="391"/>
+      <c r="V122" s="391"/>
+      <c r="W122" s="391"/>
+      <c r="X122" s="391"/>
+      <c r="Y122" s="391"/>
+      <c r="Z122" s="391"/>
+      <c r="AA122" s="391"/>
+      <c r="AB122" s="391"/>
+      <c r="AC122" s="391"/>
+      <c r="AD122" s="391"/>
+      <c r="AE122" s="391"/>
+      <c r="AF122" s="391"/>
+      <c r="AG122" s="391"/>
+      <c r="AH122" s="391"/>
+      <c r="AI122" s="391"/>
+      <c r="AJ122" s="391"/>
+      <c r="AK122" s="391"/>
+      <c r="AL122" s="391"/>
+      <c r="AM122" s="391"/>
+      <c r="AN122" s="391"/>
+      <c r="AO122" s="391"/>
+      <c r="AP122" s="391"/>
+      <c r="AQ122" s="391"/>
+      <c r="AR122" s="391"/>
+      <c r="AS122" s="391"/>
+      <c r="AT122" s="392"/>
       <c r="AU122" s="62"/>
       <c r="AZ122" s="94"/>
     </row>
@@ -10752,12 +10768,12 @@
       <c r="F124" s="60"/>
       <c r="G124" s="60"/>
       <c r="H124" s="101"/>
-      <c r="I124" s="380"/>
-      <c r="J124" s="380"/>
-      <c r="K124" s="380"/>
-      <c r="L124" s="380"/>
-      <c r="M124" s="380"/>
-      <c r="N124" s="380"/>
+      <c r="I124" s="381"/>
+      <c r="J124" s="381"/>
+      <c r="K124" s="381"/>
+      <c r="L124" s="381"/>
+      <c r="M124" s="381"/>
+      <c r="N124" s="381"/>
       <c r="O124" s="61"/>
       <c r="P124" s="61"/>
       <c r="Q124" s="100"/>
@@ -10768,13 +10784,13 @@
       <c r="V124" s="61"/>
       <c r="W124" s="61"/>
       <c r="X124" s="101"/>
-      <c r="Y124" s="380"/>
-      <c r="Z124" s="380"/>
-      <c r="AA124" s="380"/>
-      <c r="AB124" s="380"/>
-      <c r="AC124" s="380"/>
-      <c r="AD124" s="380"/>
-      <c r="AE124" s="380"/>
+      <c r="Y124" s="381"/>
+      <c r="Z124" s="381"/>
+      <c r="AA124" s="381"/>
+      <c r="AB124" s="381"/>
+      <c r="AC124" s="381"/>
+      <c r="AD124" s="381"/>
+      <c r="AE124" s="381"/>
       <c r="AF124" s="100"/>
       <c r="AG124" s="100"/>
       <c r="AH124" s="61"/>
@@ -10785,16 +10801,16 @@
       <c r="AM124" s="101" t="s">
         <v>35</v>
       </c>
-      <c r="AN124" s="385">
+      <c r="AN124" s="386">
         <f>+J37</f>
         <v>386128219</v>
       </c>
-      <c r="AO124" s="386"/>
-      <c r="AP124" s="386"/>
-      <c r="AQ124" s="386"/>
-      <c r="AR124" s="386"/>
-      <c r="AS124" s="386"/>
-      <c r="AT124" s="387"/>
+      <c r="AO124" s="387"/>
+      <c r="AP124" s="387"/>
+      <c r="AQ124" s="387"/>
+      <c r="AR124" s="387"/>
+      <c r="AS124" s="387"/>
+      <c r="AT124" s="388"/>
       <c r="AU124" s="62"/>
       <c r="AZ124" s="94">
         <v>22200000</v>
@@ -10872,16 +10888,16 @@
       <c r="AM126" s="101" t="s">
         <v>36</v>
       </c>
-      <c r="AN126" s="363">
+      <c r="AN126" s="364">
         <f>+AN113</f>
         <v>27331418.760000002</v>
       </c>
-      <c r="AO126" s="364"/>
-      <c r="AP126" s="364"/>
-      <c r="AQ126" s="364"/>
-      <c r="AR126" s="364"/>
-      <c r="AS126" s="364"/>
-      <c r="AT126" s="365"/>
+      <c r="AO126" s="365"/>
+      <c r="AP126" s="365"/>
+      <c r="AQ126" s="365"/>
+      <c r="AR126" s="365"/>
+      <c r="AS126" s="365"/>
+      <c r="AT126" s="366"/>
       <c r="AU126" s="62"/>
       <c r="AZ126" s="94">
         <f>+AZ119-AZ124</f>
@@ -10948,16 +10964,16 @@
       <c r="AM128" s="101" t="s">
         <v>38</v>
       </c>
-      <c r="AN128" s="363">
+      <c r="AN128" s="364">
         <f>SUM(AN118:AT118)</f>
-        <v>22200000</v>
-      </c>
-      <c r="AO128" s="364"/>
-      <c r="AP128" s="364"/>
-      <c r="AQ128" s="364"/>
-      <c r="AR128" s="364"/>
-      <c r="AS128" s="364"/>
-      <c r="AT128" s="365"/>
+        <v>42000000</v>
+      </c>
+      <c r="AO128" s="365"/>
+      <c r="AP128" s="365"/>
+      <c r="AQ128" s="365"/>
+      <c r="AR128" s="365"/>
+      <c r="AS128" s="365"/>
+      <c r="AT128" s="366"/>
       <c r="AU128" s="62"/>
       <c r="AZ128" s="94">
         <f>+AZ126-AZ127</f>
@@ -11011,16 +11027,16 @@
       <c r="AM130" s="101" t="s">
         <v>37</v>
       </c>
-      <c r="AN130" s="363">
+      <c r="AN130" s="364">
         <f>AN124-(AN126+AN128)</f>
-        <v>336596800.24000001</v>
-      </c>
-      <c r="AO130" s="364"/>
-      <c r="AP130" s="364"/>
-      <c r="AQ130" s="364"/>
-      <c r="AR130" s="364"/>
-      <c r="AS130" s="364"/>
-      <c r="AT130" s="365"/>
+        <v>316796800.24000001</v>
+      </c>
+      <c r="AO130" s="365"/>
+      <c r="AP130" s="365"/>
+      <c r="AQ130" s="365"/>
+      <c r="AR130" s="365"/>
+      <c r="AS130" s="365"/>
+      <c r="AT130" s="366"/>
       <c r="AU130" s="62"/>
       <c r="AZ130" s="103">
         <f>+AN42</f>
@@ -11113,13 +11129,13 @@
       <c r="AM132" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="AN132" s="382"/>
-      <c r="AO132" s="383"/>
-      <c r="AP132" s="383"/>
-      <c r="AQ132" s="383"/>
-      <c r="AR132" s="383"/>
-      <c r="AS132" s="383"/>
-      <c r="AT132" s="384"/>
+      <c r="AN132" s="383"/>
+      <c r="AO132" s="384"/>
+      <c r="AP132" s="384"/>
+      <c r="AQ132" s="384"/>
+      <c r="AR132" s="384"/>
+      <c r="AS132" s="384"/>
+      <c r="AT132" s="385"/>
       <c r="AU132" s="14"/>
       <c r="AZ132" s="56">
         <v>54000000</v>
@@ -11143,21 +11159,21 @@
       <c r="O133" s="19"/>
       <c r="P133" s="19"/>
       <c r="Q133" s="19"/>
-      <c r="AA133" s="375" t="s">
+      <c r="AA133" s="376" t="s">
         <v>97</v>
       </c>
-      <c r="AB133" s="375"/>
-      <c r="AC133" s="375"/>
-      <c r="AD133" s="375"/>
-      <c r="AE133" s="375"/>
-      <c r="AF133" s="375"/>
-      <c r="AG133" s="375"/>
-      <c r="AH133" s="375"/>
-      <c r="AI133" s="375"/>
-      <c r="AJ133" s="375"/>
-      <c r="AK133" s="375"/>
-      <c r="AL133" s="375"/>
-      <c r="AM133" s="375"/>
+      <c r="AB133" s="376"/>
+      <c r="AC133" s="376"/>
+      <c r="AD133" s="376"/>
+      <c r="AE133" s="376"/>
+      <c r="AF133" s="376"/>
+      <c r="AG133" s="376"/>
+      <c r="AH133" s="376"/>
+      <c r="AI133" s="376"/>
+      <c r="AJ133" s="376"/>
+      <c r="AK133" s="376"/>
+      <c r="AL133" s="376"/>
+      <c r="AM133" s="376"/>
       <c r="AU133" s="14"/>
       <c r="AZ133" s="57">
         <f>+AZ131-AZ132</f>
@@ -11183,15 +11199,15 @@
       <c r="AK134" s="2"/>
       <c r="AL134" s="2"/>
       <c r="AM134" s="1"/>
-      <c r="AN134" s="377" t="s">
+      <c r="AN134" s="378" t="s">
         <v>58</v>
       </c>
-      <c r="AO134" s="377"/>
-      <c r="AP134" s="377"/>
-      <c r="AQ134" s="377"/>
-      <c r="AR134" s="377"/>
-      <c r="AS134" s="377"/>
-      <c r="AT134" s="377"/>
+      <c r="AO134" s="378"/>
+      <c r="AP134" s="378"/>
+      <c r="AQ134" s="378"/>
+      <c r="AR134" s="378"/>
+      <c r="AS134" s="378"/>
+      <c r="AT134" s="378"/>
       <c r="AU134" s="14"/>
       <c r="AZ134" s="56">
         <v>29596800</v>
@@ -11211,19 +11227,19 @@
       <c r="I135" s="135"/>
       <c r="J135" s="135"/>
       <c r="K135" s="135"/>
-      <c r="L135" s="379" t="s">
-        <v>138</v>
-      </c>
-      <c r="M135" s="379"/>
-      <c r="N135" s="379"/>
-      <c r="O135" s="379"/>
-      <c r="P135" s="379"/>
-      <c r="Q135" s="379"/>
-      <c r="R135" s="379"/>
-      <c r="S135" s="379"/>
-      <c r="T135" s="379"/>
-      <c r="U135" s="379"/>
-      <c r="V135" s="379"/>
+      <c r="L135" s="380" t="s">
+        <v>136</v>
+      </c>
+      <c r="M135" s="380"/>
+      <c r="N135" s="380"/>
+      <c r="O135" s="380"/>
+      <c r="P135" s="380"/>
+      <c r="Q135" s="380"/>
+      <c r="R135" s="380"/>
+      <c r="S135" s="380"/>
+      <c r="T135" s="380"/>
+      <c r="U135" s="380"/>
+      <c r="V135" s="380"/>
       <c r="W135" s="31"/>
       <c r="X135" s="33" t="s">
         <v>82</v>
@@ -11329,7 +11345,7 @@
       <c r="J137" s="115"/>
       <c r="K137" s="115"/>
       <c r="L137" s="117" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="M137" s="117"/>
       <c r="N137" s="117"/>
@@ -11352,7 +11368,7 @@
       <c r="AC137" s="55"/>
       <c r="AD137" s="31"/>
       <c r="AE137" s="118" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AF137" s="119"/>
       <c r="AG137" s="50"/>
@@ -11817,7 +11833,7 @@
         <v>40</v>
       </c>
       <c r="AD147" s="112" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AE147" s="112"/>
       <c r="AF147" s="112"/>
@@ -11870,7 +11886,7 @@
         <v>41</v>
       </c>
       <c r="AD148" s="112" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AE148" s="112"/>
       <c r="AF148" s="112"/>
